--- a/backend/data/job-applications.xlsx
+++ b/backend/data/job-applications.xlsx
@@ -828,7 +828,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I333"/>
+  <dimension ref="A1:I353"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -10498,9 +10498,589 @@
         <v>External — apply manually</v>
       </c>
     </row>
+    <row r="334">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334" t="str">
+        <v>2/9/2026, 12:49:56 pm</v>
+      </c>
+      <c r="C334" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D334" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E334" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F334" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G334" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-310826920170</v>
+      </c>
+      <c r="H334" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-310826920170</v>
+      </c>
+      <c r="I334" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335" t="str">
+        <v>2/9/2026, 12:50:01 pm</v>
+      </c>
+      <c r="C335" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D335" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E335" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F335" t="str">
+        <v>Hyderabad, Mumbai</v>
+      </c>
+      <c r="G335" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-mumbai-hyderabad-2-to-5-years-170826921174</v>
+      </c>
+      <c r="H335" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-mumbai-hyderabad-2-to-5-years-170826921174</v>
+      </c>
+      <c r="I335" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336" t="str">
+        <v>2/9/2026, 12:50:06 pm</v>
+      </c>
+      <c r="C336" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D336" t="str">
+        <v>Software Development Engineer</v>
+      </c>
+      <c r="E336" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F336" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G336" t="str">
+        <v>https://www.naukri.com/job-listings-software-development-engineer-accenture-solutions-pvt-ltd-hyderabad-1-to-4-years-170826923848</v>
+      </c>
+      <c r="H336" t="str">
+        <v>https://www.naukri.com/job-listings-software-development-engineer-accenture-solutions-pvt-ltd-hyderabad-1-to-4-years-170826923848</v>
+      </c>
+      <c r="I336" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>336</v>
+      </c>
+      <c r="B337" t="str">
+        <v>2/9/2026, 12:50:10 pm</v>
+      </c>
+      <c r="C337" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D337" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E337" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F337" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G337" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-310826918711</v>
+      </c>
+      <c r="H337" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-310826918711</v>
+      </c>
+      <c r="I337" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>337</v>
+      </c>
+      <c r="B338" t="str">
+        <v>2/9/2026, 12:50:15 pm</v>
+      </c>
+      <c r="C338" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D338" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E338" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F338" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G338" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-310826917881</v>
+      </c>
+      <c r="H338" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-310826917881</v>
+      </c>
+      <c r="I338" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>338</v>
+      </c>
+      <c r="B339" t="str">
+        <v>2/9/2026, 12:50:19 pm</v>
+      </c>
+      <c r="C339" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D339" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E339" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F339" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G339" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-010926932687</v>
+      </c>
+      <c r="H339" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-010926932687</v>
+      </c>
+      <c r="I339" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>339</v>
+      </c>
+      <c r="B340" t="str">
+        <v>2/9/2026, 12:50:24 pm</v>
+      </c>
+      <c r="C340" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D340" t="str">
+        <v>Java Developer Spring Boot Flink &amp; Kafka</v>
+      </c>
+      <c r="E340" t="str">
+        <v>Stellar Technologies</v>
+      </c>
+      <c r="F340" t="str">
+        <v>Hyderabad, Mumbai, Kolkata, New Delhi, Pune, Chennai, Bengaluru</v>
+      </c>
+      <c r="G340" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-spring-boot-flink-kafka-stellar-technologies-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-4-years-220525505217</v>
+      </c>
+      <c r="H340" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-spring-boot-flink-kafka-stellar-technologies-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-4-years-220525505217</v>
+      </c>
+      <c r="I340" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>340</v>
+      </c>
+      <c r="B341" t="str">
+        <v>2/9/2026, 12:50:28 pm</v>
+      </c>
+      <c r="C341" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D341" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E341" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F341" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G341" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-5-years-310826918541</v>
+      </c>
+      <c r="H341" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-5-years-310826918541</v>
+      </c>
+      <c r="I341" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>341</v>
+      </c>
+      <c r="B342" t="str">
+        <v>2/9/2026, 12:50:33 pm</v>
+      </c>
+      <c r="C342" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D342" t="str">
+        <v>Application Developer-Cloud FullStack</v>
+      </c>
+      <c r="E342" t="str">
+        <v>IBM</v>
+      </c>
+      <c r="F342" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G342" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-cloud-fullstack-ibm-india-pvt-limited-hyderabad-3-to-8-years-260826923637</v>
+      </c>
+      <c r="H342" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-cloud-fullstack-ibm-india-pvt-limited-hyderabad-3-to-8-years-260826923637</v>
+      </c>
+      <c r="I342" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>342</v>
+      </c>
+      <c r="B343" t="str">
+        <v>2/9/2026, 12:50:38 pm</v>
+      </c>
+      <c r="C343" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D343" t="str">
+        <v>Full Stack Developer - Java</v>
+      </c>
+      <c r="E343" t="str">
+        <v>Proounce</v>
+      </c>
+      <c r="F343" t="str">
+        <v>Hyderabad, Mumbai, Kolkata, New Delhi, Pune, Chennai, Bengaluru</v>
+      </c>
+      <c r="G343" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-java-proounce-solutions-private-limited-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-6-to-10-years-141024501812</v>
+      </c>
+      <c r="H343" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-java-proounce-solutions-private-limited-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-6-to-10-years-141024501812</v>
+      </c>
+      <c r="I343" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>343</v>
+      </c>
+      <c r="B344" t="str">
+        <v>2/9/2026, 12:50:42 pm</v>
+      </c>
+      <c r="C344" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D344" t="str">
+        <v>Full Stack Developer - Project Alpha</v>
+      </c>
+      <c r="E344" t="str">
+        <v>Avataa Solutions</v>
+      </c>
+      <c r="F344" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G344" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-project-alpha-avataa-solutions-hyderabad-3-to-7-years-150526502877</v>
+      </c>
+      <c r="H344" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-project-alpha-avataa-solutions-hyderabad-3-to-7-years-150526502877</v>
+      </c>
+      <c r="I344" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345" t="str">
+        <v>2/9/2026, 12:50:47 pm</v>
+      </c>
+      <c r="C345" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D345" t="str">
+        <v>AI Augmented Full Stack Engineer</v>
+      </c>
+      <c r="E345" t="str">
+        <v>I5 Systems</v>
+      </c>
+      <c r="F345" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G345" t="str">
+        <v>https://www.naukri.com/job-listings-ai-augmented-full-stack-engineer-i5-systems-hyderabad-3-to-7-years-010526502998</v>
+      </c>
+      <c r="H345" t="str">
+        <v>https://www.naukri.com/job-listings-ai-augmented-full-stack-engineer-i5-systems-hyderabad-3-to-7-years-010526502998</v>
+      </c>
+      <c r="I345" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346" t="str">
+        <v>2/9/2026, 12:50:51 pm</v>
+      </c>
+      <c r="C346" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D346" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E346" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F346" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G346" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-240826926095</v>
+      </c>
+      <c r="H346" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-240826926095</v>
+      </c>
+      <c r="I346" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347" t="str">
+        <v>2/9/2026, 12:50:56 pm</v>
+      </c>
+      <c r="C347" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D347" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E347" t="str">
+        <v>Annnetwork</v>
+      </c>
+      <c r="F347" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G347" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-annnetwork-hyderabad-3-to-5-years-121125501120</v>
+      </c>
+      <c r="H347" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-annnetwork-hyderabad-3-to-5-years-121125501120</v>
+      </c>
+      <c r="I347" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348" t="str">
+        <v>2/9/2026, 12:51:00 pm</v>
+      </c>
+      <c r="C348" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D348" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E348" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F348" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G348" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-110826934178</v>
+      </c>
+      <c r="H348" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-110826934178</v>
+      </c>
+      <c r="I348" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349" t="str">
+        <v>2/9/2026, 12:51:05 pm</v>
+      </c>
+      <c r="C349" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D349" t="str">
+        <v>Java + React Full Stack Developer</v>
+      </c>
+      <c r="E349" t="str">
+        <v>Orbion Infotech</v>
+      </c>
+      <c r="F349" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G349" t="str">
+        <v>https://www.naukri.com/job-listings-java-react-full-stack-developer-orbion-infotech-hyderabad-7-to-8-years-010926503869</v>
+      </c>
+      <c r="H349" t="str">
+        <v>https://www.naukri.com/job-listings-java-react-full-stack-developer-orbion-infotech-hyderabad-7-to-8-years-010926503869</v>
+      </c>
+      <c r="I349" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350" t="str">
+        <v>2/9/2026, 12:51:10 pm</v>
+      </c>
+      <c r="C350" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D350" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E350" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F350" t="str">
+        <v>Hyderabad, Mumbai</v>
+      </c>
+      <c r="G350" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-mumbai-hyderabad-3-to-8-years-110826931532</v>
+      </c>
+      <c r="H350" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-mumbai-hyderabad-3-to-8-years-110826931532</v>
+      </c>
+      <c r="I350" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351" t="str">
+        <v>2/9/2026, 12:51:14 pm</v>
+      </c>
+      <c r="C351" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D351" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E351" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F351" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G351" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-170826925605</v>
+      </c>
+      <c r="H351" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-170826925605</v>
+      </c>
+      <c r="I351" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352" t="str">
+        <v>2/9/2026, 12:51:19 pm</v>
+      </c>
+      <c r="C352" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D352" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E352" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F352" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G352" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-170826924949</v>
+      </c>
+      <c r="H352" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-170826924949</v>
+      </c>
+      <c r="I352" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353" t="str">
+        <v>2/9/2026, 12:51:23 pm</v>
+      </c>
+      <c r="C353" t="str">
+        <v>naukri_external</v>
+      </c>
+      <c r="D353" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E353" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F353" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G353" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-310826918599</v>
+      </c>
+      <c r="H353" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-310826918599</v>
+      </c>
+      <c r="I353" t="str">
+        <v>Captured form state (0 fields)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I333"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I353"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/backend/data/job-applications.xlsx
+++ b/backend/data/job-applications.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -819,9 +819,38 @@
         <v>Naukri quick-apply (auto)</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2/9/2026, 5:12:38 pm</v>
+      </c>
+      <c r="C15" t="str">
+        <v>manual_external</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Google</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G15" t="str">
+        <v>https://careers.google.com/jobs/123</v>
+      </c>
+      <c r="H15" t="str">
+        <v>https://careers.google.com/jobs/123</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Applied via Google Careers</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/backend/data/job-applications.xlsx
+++ b/backend/data/job-applications.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I38"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -848,16 +848,683 @@
         <v>Applied via Google Careers</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>3/9/2026, 11:35:51 am</v>
+      </c>
+      <c r="C16" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Java Full Stack Developer - Java + Angular</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Epam Systems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Hybrid - Hyderabad, Gurugram, Bengaluru</v>
+      </c>
+      <c r="G16" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-java-angular-epam-systems-hyderabad-gurugram-bengaluru-5-to-10-years-020926012103</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>3/9/2026, 11:36:38 am</v>
+      </c>
+      <c r="C17" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Mspc Services</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="G17" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-mspc-services-hyderabad-india-7-to-14-years-020926035061</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>3/9/2026, 11:37:30 am</v>
+      </c>
+      <c r="C18" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Purview Services</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Hyderabad, Pune</v>
+      </c>
+      <c r="G18" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-purview-services-hyderabad-pune-7-to-11-years-020926023873</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>3/9/2026, 11:40:02 am</v>
+      </c>
+      <c r="C19" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Hiringeye Solutions</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G19" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-hiringeye-solutions-hyderabad-5-to-7-years-020926030624</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>3/9/2026, 11:40:54 am</v>
+      </c>
+      <c r="C20" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Tech Mahindra</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G20" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tech-mahindra-hyderabad-bengaluru-4-to-7-years-010926021313</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>3/9/2026, 11:41:19 am</v>
+      </c>
+      <c r="C21" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Java Full Stack Developer - Principal Software Engineer</v>
+      </c>
+      <c r="E21" t="str">
+        <v>My Compliance Office</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G21" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-principal-software-engineer-my-compliance-office-hyderabad-10-to-15-years-010926013277</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>3/9/2026, 11:41:27 am</v>
+      </c>
+      <c r="C22" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Java Full Stack Developer with Angular/React.JS</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Hexaware Technologies</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Hybrid - Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G22" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-with-angular-react-js-hexaware-technologies-hyderabad-pune-bengaluru-6-to-11-years-270426024249</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>3/9/2026, 11:41:35 am</v>
+      </c>
+      <c r="C23" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E23" t="str">
+        <v>IPS group</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G23" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-integrated-personnel-services-hyderabad-chennai-bengaluru-7-to-11-years-250826024457</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>3/9/2026, 11:41:44 am</v>
+      </c>
+      <c r="C24" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Java Full Stack Developer (C2H)</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Hybrid - Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G24" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-c2h-srs-infoway-hyderabad-pune-bengaluru-7-to-10-years-250826020109</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>3/9/2026, 11:41:52 am</v>
+      </c>
+      <c r="C25" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E25" t="str">
+        <v>CGI</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Hybrid - Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G25" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cgi-hyderabad-bengaluru-5-to-10-years-210826024027</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>3/9/2026, 11:43:45 am</v>
+      </c>
+      <c r="C26" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Java Full Stack Developer-</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G26" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tata-consultancy-services-hyderabad-7-to-12-years-070826038971</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>3/9/2026, 11:44:59 am</v>
+      </c>
+      <c r="C27" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Cloudxtreme</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G27" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cloudxtreme-hyderabad-chennai-bengaluru-6-to-11-years-210826004489</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>3/9/2026, 11:45:32 am</v>
+      </c>
+      <c r="C28" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E28" t="str">
+        <v>CGI</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G28" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cgi-hyderabad-6-to-8-years-190826037969</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>3/9/2026, 11:45:48 am</v>
+      </c>
+      <c r="C29" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Cloudxtreme</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G29" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cloudxtreme-hyderabad-bengaluru-5-to-10-years-190826033518</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>3/9/2026, 11:46:35 am</v>
+      </c>
+      <c r="C30" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G30" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-infosys-hyderabad-pune-bengaluru-8-to-10-years-261225027018</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>3/9/2026, 11:46:51 am</v>
+      </c>
+      <c r="C31" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Java Full Stack Developer (Java + React)</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Hybrid - Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G31" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-java-react-capgemini-hyderabad-bengaluru-5-to-8-years-250826030358</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>3/9/2026, 11:47:06 am</v>
+      </c>
+      <c r="C32" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G32" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-bengaluru-6-to-10-years-200826012802</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>3/9/2026, 11:47:44 am</v>
+      </c>
+      <c r="C33" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Java Full Stack Developer - (Angular or React)</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G33" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-angular-or-react-infosys-hyderabad-chennai-bengaluru-6-to-11-years-270826028634</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>3/9/2026, 11:47:52 am</v>
+      </c>
+      <c r="C34" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Hybrid - Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G34" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-pune-bengaluru-6-to-9-years-100626030945</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>3/9/2026, 11:47:59 am</v>
+      </c>
+      <c r="C35" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E35" t="str">
+        <v>G R Consultants</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G35" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-g-r-consultants-hyderabad-chennai-bengaluru-7-to-12-years-130826021589</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>3/9/2026, 11:48:16 am</v>
+      </c>
+      <c r="C36" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Tekskills</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G36" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-hyderabad-8-to-10-years-110826036980</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>3/9/2026, 11:48:59 am</v>
+      </c>
+      <c r="C37" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E37" t="str">
+        <v>People Impact</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G37" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-people-impact-hyderabad-4-to-6-years-050826036971</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>3/9/2026, 11:49:15 am</v>
+      </c>
+      <c r="C38" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Optum</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Hybrid - Hyderabad, Noida</v>
+      </c>
+      <c r="G38" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-optum-noida-hyderabad-4-to-7-years-030826004693</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>Naukri quick-apply (auto)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I38"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I333"/>
+  <dimension ref="A1:I369"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -10527,9 +11194,1053 @@
         <v>Captured form state (0 fields)</v>
       </c>
     </row>
+    <row r="334">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334" t="str">
+        <v>3/9/2026, 11:38:01 am</v>
+      </c>
+      <c r="C334" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D334" t="str">
+        <v>Lead Java Full Stack Developer</v>
+      </c>
+      <c r="E334" t="str">
+        <v>GE Vernova Consulting</v>
+      </c>
+      <c r="F334" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G334" t="str">
+        <v>https://www.naukri.com/job-listings-lead-java-full-stack-developer-ge-vernova-consulting-hyderabad-5-to-10-years-010926504843</v>
+      </c>
+      <c r="H334" t="str">
+        <v>https://www.naukri.com/job-listings-lead-java-full-stack-developer-ge-vernova-consulting-hyderabad-5-to-10-years-010926504843</v>
+      </c>
+      <c r="I334" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335" t="str">
+        <v>3/9/2026, 11:38:22 am</v>
+      </c>
+      <c r="C335" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D335" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E335" t="str">
+        <v>Aptsol Global Tech</v>
+      </c>
+      <c r="F335" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G335" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-aptsol-global-tech-pvt-ltd-hyderabad-3-to-5-years-120724501688</v>
+      </c>
+      <c r="H335" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-aptsol-global-tech-pvt-ltd-hyderabad-3-to-5-years-120724501688</v>
+      </c>
+      <c r="I335" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336" t="str">
+        <v>3/9/2026, 11:39:47 am</v>
+      </c>
+      <c r="C336" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D336" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E336" t="str">
+        <v>Pragma Edge Software Services</v>
+      </c>
+      <c r="F336" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G336" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-pragma-edge-software-services-private-limited-hyderabad-2-to-5-years-290124502269</v>
+      </c>
+      <c r="H336" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-pragma-edge-software-services-private-limited-hyderabad-2-to-5-years-290124502269</v>
+      </c>
+      <c r="I336" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>336</v>
+      </c>
+      <c r="B337" t="str">
+        <v>3/9/2026, 11:40:58 am</v>
+      </c>
+      <c r="C337" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D337" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E337" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F337" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G337" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-010926930334</v>
+      </c>
+      <c r="H337" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-010926930334</v>
+      </c>
+      <c r="I337" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>337</v>
+      </c>
+      <c r="B338" t="str">
+        <v>3/9/2026, 11:43:26 am</v>
+      </c>
+      <c r="C338" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D338" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E338" t="str">
+        <v>Leuwint Technologies</v>
+      </c>
+      <c r="F338" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G338" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-leuwint-technologies-hyderabad-9-to-14-years-310826503707</v>
+      </c>
+      <c r="H338" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-leuwint-technologies-hyderabad-9-to-14-years-310826503707</v>
+      </c>
+      <c r="I338" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>338</v>
+      </c>
+      <c r="B339" t="str">
+        <v>3/9/2026, 11:43:38 am</v>
+      </c>
+      <c r="C339" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D339" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E339" t="str">
+        <v>Alladi Cloud Training Institute</v>
+      </c>
+      <c r="F339" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G339" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-alladi-cloud-training-hyderabad-6-to-10-years-180226503914</v>
+      </c>
+      <c r="H339" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-alladi-cloud-training-hyderabad-6-to-10-years-180226503914</v>
+      </c>
+      <c r="I339" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>339</v>
+      </c>
+      <c r="B340" t="str">
+        <v>3/9/2026, 11:43:49 am</v>
+      </c>
+      <c r="C340" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D340" t="str">
+        <v>Java Full Stack Developer - Fresher</v>
+      </c>
+      <c r="E340" t="str">
+        <v>Zyphra Tech Solutions</v>
+      </c>
+      <c r="F340" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G340" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-fresher-zyphra-tech-solutions-inc-hyderabad-0-to-2-years-080626502238</v>
+      </c>
+      <c r="H340" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-fresher-zyphra-tech-solutions-inc-hyderabad-0-to-2-years-080626502238</v>
+      </c>
+      <c r="I340" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>340</v>
+      </c>
+      <c r="B341" t="str">
+        <v>3/9/2026, 11:49:19 am</v>
+      </c>
+      <c r="C341" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D341" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E341" t="str">
+        <v>IDESLABS</v>
+      </c>
+      <c r="F341" t="str">
+        <v>Hyderabad, Mumbai, Kolkata, New Delhi, Pune, Chennai, Bengaluru</v>
+      </c>
+      <c r="G341" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-ideslabs-private-limited-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-4-to-6-years-071223501188</v>
+      </c>
+      <c r="H341" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-ideslabs-private-limited-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-4-to-6-years-071223501188</v>
+      </c>
+      <c r="I341" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>341</v>
+      </c>
+      <c r="B342" t="str">
+        <v>3/9/2026, 11:49:23 am</v>
+      </c>
+      <c r="C342" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D342" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E342" t="str">
+        <v>Mobigesture Software</v>
+      </c>
+      <c r="F342" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G342" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-mobigesture-hyderabad-4-to-8-years-311025500779</v>
+      </c>
+      <c r="H342" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-mobigesture-hyderabad-4-to-8-years-311025500779</v>
+      </c>
+      <c r="I342" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>342</v>
+      </c>
+      <c r="B343" t="str">
+        <v>3/9/2026, 11:49:27 am</v>
+      </c>
+      <c r="C343" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D343" t="str">
+        <v>Java Full Stack Developer-AWS</v>
+      </c>
+      <c r="E343" t="str">
+        <v>Han Digital Solution</v>
+      </c>
+      <c r="F343" t="str">
+        <v>Hyderabad, Warangal, Nizamabad</v>
+      </c>
+      <c r="G343" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-aws-han-digital-solution-warangal-hyderabad-nizamabad-5-to-9-years-221125501089</v>
+      </c>
+      <c r="H343" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-aws-han-digital-solution-warangal-hyderabad-nizamabad-5-to-9-years-221125501089</v>
+      </c>
+      <c r="I343" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>343</v>
+      </c>
+      <c r="B344" t="str">
+        <v>3/9/2026, 11:49:31 am</v>
+      </c>
+      <c r="C344" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D344" t="str">
+        <v>Java Full stack Developer with Angular/React</v>
+      </c>
+      <c r="E344" t="str">
+        <v>Crisil</v>
+      </c>
+      <c r="F344" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G344" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-with-angular-react-crisil-hyderabad-8-to-12-years-220526500508</v>
+      </c>
+      <c r="H344" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-with-angular-react-crisil-hyderabad-8-to-12-years-220526500508</v>
+      </c>
+      <c r="I344" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345" t="str">
+        <v>3/9/2026, 11:49:35 am</v>
+      </c>
+      <c r="C345" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D345" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E345" t="str">
+        <v>Trisun Technologies And Services</v>
+      </c>
+      <c r="F345" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G345" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-trisun-technologies-and-services-hyderabad-8-to-13-years-190325510153</v>
+      </c>
+      <c r="H345" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-trisun-technologies-and-services-hyderabad-8-to-13-years-190325510153</v>
+      </c>
+      <c r="I345" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346" t="str">
+        <v>3/9/2026, 11:54:44 am</v>
+      </c>
+      <c r="C346" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D346" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E346" t="str">
+        <v>Nbits</v>
+      </c>
+      <c r="F346" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G346" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-nbits-hyderabad-5-to-10-years-060325502001</v>
+      </c>
+      <c r="H346" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-nbits-hyderabad-5-to-10-years-060325502001</v>
+      </c>
+      <c r="I346" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347" t="str">
+        <v>3/9/2026, 11:54:56 am</v>
+      </c>
+      <c r="C347" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D347" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E347" t="str">
+        <v>Pronix It Solutions</v>
+      </c>
+      <c r="F347" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G347" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-pronix-inc-hyderabad-4-to-5-years-040526500240</v>
+      </c>
+      <c r="H347" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-pronix-inc-hyderabad-4-to-5-years-040526500240</v>
+      </c>
+      <c r="I347" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348" t="str">
+        <v>3/9/2026, 11:55:08 am</v>
+      </c>
+      <c r="C348" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D348" t="str">
+        <v>Senior Java Full Stack Developer</v>
+      </c>
+      <c r="E348" t="str">
+        <v>Vrize</v>
+      </c>
+      <c r="F348" t="str">
+        <v>Hyderabad, Mumbai, Kolkata, New Delhi, Pune, Chennai, Bengaluru</v>
+      </c>
+      <c r="G348" t="str">
+        <v>https://www.naukri.com/job-listings-senior-java-full-stack-developer-vrize-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-4-to-9-years-120725502814</v>
+      </c>
+      <c r="H348" t="str">
+        <v>https://www.naukri.com/job-listings-senior-java-full-stack-developer-vrize-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-4-to-9-years-120725502814</v>
+      </c>
+      <c r="I348" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349" t="str">
+        <v>3/9/2026, 11:55:36 am</v>
+      </c>
+      <c r="C349" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D349" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E349" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F349" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G349" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-240826925964</v>
+      </c>
+      <c r="H349" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-240826925964</v>
+      </c>
+      <c r="I349" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350" t="str">
+        <v>3/9/2026, 11:55:40 am</v>
+      </c>
+      <c r="C350" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D350" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E350" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F350" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G350" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-240826925272</v>
+      </c>
+      <c r="H350" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-240826925272</v>
+      </c>
+      <c r="I350" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351" t="str">
+        <v>3/9/2026, 11:58:49 am</v>
+      </c>
+      <c r="C351" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D351" t="str">
+        <v>Senior Java Full Stack Developer</v>
+      </c>
+      <c r="E351" t="str">
+        <v>Whopper Technologies</v>
+      </c>
+      <c r="F351" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G351" t="str">
+        <v>https://www.naukri.com/job-listings-senior-java-full-stack-developer-whopper-technologies-hyderabad-5-to-9-years-270325501262</v>
+      </c>
+      <c r="H351" t="str">
+        <v>https://www.naukri.com/job-listings-senior-java-full-stack-developer-whopper-technologies-hyderabad-5-to-9-years-270325501262</v>
+      </c>
+      <c r="I351" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352" t="str">
+        <v>3/9/2026, 11:58:53 am</v>
+      </c>
+      <c r="C352" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D352" t="str">
+        <v>Senior Java Full Stack Developer</v>
+      </c>
+      <c r="E352" t="str">
+        <v>Mindtris</v>
+      </c>
+      <c r="F352" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G352" t="str">
+        <v>https://www.naukri.com/job-listings-senior-java-full-stack-developer-mindtris-hyderabad-5-to-10-years-040225503084</v>
+      </c>
+      <c r="H352" t="str">
+        <v>https://www.naukri.com/job-listings-senior-java-full-stack-developer-mindtris-hyderabad-5-to-10-years-040225503084</v>
+      </c>
+      <c r="I352" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353" t="str">
+        <v>3/9/2026, 11:59:53 am</v>
+      </c>
+      <c r="C353" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D353" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E353" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F353" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G353" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-190826915063</v>
+      </c>
+      <c r="H353" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-190826915063</v>
+      </c>
+      <c r="I353" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354" t="str">
+        <v>3/9/2026, 12:01:25 pm</v>
+      </c>
+      <c r="C354" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D354" t="str">
+        <v>Java Full-Stack Developer</v>
+      </c>
+      <c r="E354" t="str">
+        <v>Oracle Information Systems</v>
+      </c>
+      <c r="F354" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G354" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-oracle-information-systems-hyderabad-5-to-8-years-310720500599</v>
+      </c>
+      <c r="H354" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-oracle-information-systems-hyderabad-5-to-8-years-310720500599</v>
+      </c>
+      <c r="I354" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355" t="str">
+        <v>3/9/2026, 12:01:53 pm</v>
+      </c>
+      <c r="C355" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D355" t="str">
+        <v>Java Full stack Developer with Angular</v>
+      </c>
+      <c r="E355" t="str">
+        <v>Devlats</v>
+      </c>
+      <c r="F355" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G355" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-with-angular-devlats-hyderabad-4-to-9-years-070526501887</v>
+      </c>
+      <c r="H355" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-with-angular-devlats-hyderabad-4-to-9-years-070526501887</v>
+      </c>
+      <c r="I355" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356" t="str">
+        <v>3/9/2026, 12:02:30 pm</v>
+      </c>
+      <c r="C356" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D356" t="str">
+        <v>Java Full stack developer</v>
+      </c>
+      <c r="E356" t="str">
+        <v>Golden Future Technologies</v>
+      </c>
+      <c r="F356" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G356" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-golden-future-technologies-hyderabad-6-to-12-years-041023502100</v>
+      </c>
+      <c r="H356" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-golden-future-technologies-hyderabad-6-to-12-years-041023502100</v>
+      </c>
+      <c r="I356" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357" t="str">
+        <v>3/9/2026, 12:02:34 pm</v>
+      </c>
+      <c r="C357" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D357" t="str">
+        <v>Java Full Stack Developer (Angular)</v>
+      </c>
+      <c r="E357" t="str">
+        <v>Imedhas</v>
+      </c>
+      <c r="F357" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G357" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-angular-imedhas-consulting-services-hyderabad-4-to-8-years-040626501012</v>
+      </c>
+      <c r="H357" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-angular-imedhas-consulting-services-hyderabad-4-to-8-years-040626501012</v>
+      </c>
+      <c r="I357" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358" t="str">
+        <v>3/9/2026, 12:03:31 pm</v>
+      </c>
+      <c r="C358" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D358" t="str">
+        <v>Java + Microservices Developers</v>
+      </c>
+      <c r="E358" t="str">
+        <v>Virtualware Innovations</v>
+      </c>
+      <c r="F358" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G358" t="str">
+        <v>https://www.naukri.com/job-listings-java-microservices-developers-virtualware-innovations-hyderabad-bengaluru-3-to-7-years-020926504318</v>
+      </c>
+      <c r="H358" t="str">
+        <v>https://www.naukri.com/job-listings-java-microservices-developers-virtualware-innovations-hyderabad-bengaluru-3-to-7-years-020926504318</v>
+      </c>
+      <c r="I358" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359" t="str">
+        <v>3/9/2026, 12:03:51 pm</v>
+      </c>
+      <c r="C359" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D359" t="str">
+        <v>Senior Software Engineer</v>
+      </c>
+      <c r="E359" t="str">
+        <v>Infinite</v>
+      </c>
+      <c r="F359" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G359" t="str">
+        <v>https://www.naukri.com/job-listings-senior-software-engineer-infinite-computer-solutions-india-pvt-ltd-hyderabad-2-to-9-years-020926504137</v>
+      </c>
+      <c r="H359" t="str">
+        <v>https://www.naukri.com/job-listings-senior-software-engineer-infinite-computer-solutions-india-pvt-ltd-hyderabad-2-to-9-years-020926504137</v>
+      </c>
+      <c r="I359" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360" t="str">
+        <v>3/9/2026, 12:04:03 pm</v>
+      </c>
+      <c r="C360" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D360" t="str">
+        <v>Application Developer-Cloud FullStack</v>
+      </c>
+      <c r="E360" t="str">
+        <v>IBM</v>
+      </c>
+      <c r="F360" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G360" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-cloud-fullstack-ibm-india-pvt-limited-hyderabad-5-to-10-years-020926922773</v>
+      </c>
+      <c r="H360" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-cloud-fullstack-ibm-india-pvt-limited-hyderabad-5-to-10-years-020926922773</v>
+      </c>
+      <c r="I360" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361" t="str">
+        <v>3/9/2026, 12:06:33 pm</v>
+      </c>
+      <c r="C361" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D361" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E361" t="str">
+        <v>Technohandz Global Information Technology Consultants</v>
+      </c>
+      <c r="F361" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G361" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-technohandz-global-information-technology-consultants-l-l-c-hyderabad-4-to-9-years-240726505149</v>
+      </c>
+      <c r="H361" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-technohandz-global-information-technology-consultants-l-l-c-hyderabad-4-to-9-years-240726505149</v>
+      </c>
+      <c r="I361" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362" t="str">
+        <v>3/9/2026, 12:06:37 pm</v>
+      </c>
+      <c r="C362" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D362" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E362" t="str">
+        <v>Logic Planet</v>
+      </c>
+      <c r="F362" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G362" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-logicplanet-it-services-hyderabad-4-to-8-years-240226500272</v>
+      </c>
+      <c r="H362" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-logicplanet-it-services-hyderabad-4-to-8-years-240226500272</v>
+      </c>
+      <c r="I362" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363" t="str">
+        <v>3/9/2026, 12:06:41 pm</v>
+      </c>
+      <c r="C363" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D363" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E363" t="str">
+        <v>Peoples Growth Hr Solutions</v>
+      </c>
+      <c r="F363" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G363" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-peoples-growth-hr-solutions-pvt-ltd-hyderabad-5-to-10-years-180425503138</v>
+      </c>
+      <c r="H363" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-peoples-growth-hr-solutions-pvt-ltd-hyderabad-5-to-10-years-180425503138</v>
+      </c>
+      <c r="I363" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364" t="str">
+        <v>3/9/2026, 12:06:53 pm</v>
+      </c>
+      <c r="C364" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D364" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E364" t="str">
+        <v>Bytesedge</v>
+      </c>
+      <c r="F364" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G364" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-bytesedge-hyderabad-5-to-9-years-090823500603</v>
+      </c>
+      <c r="H364" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-bytesedge-hyderabad-5-to-9-years-090823500603</v>
+      </c>
+      <c r="I364" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365" t="str">
+        <v>3/9/2026, 12:08:17 pm</v>
+      </c>
+      <c r="C365" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D365" t="str">
+        <v>Java Developer (P&amp;C Insurance)</v>
+      </c>
+      <c r="E365" t="str">
+        <v>Blitzenx</v>
+      </c>
+      <c r="F365" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G365" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-p-c-insurance-blitzenx-rapid-consulting-services-hyderabad-5-to-10-years-130726503856</v>
+      </c>
+      <c r="H365" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-p-c-insurance-blitzenx-rapid-consulting-services-hyderabad-5-to-10-years-130726503856</v>
+      </c>
+      <c r="I365" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366" t="str">
+        <v>3/9/2026, 12:08:38 pm</v>
+      </c>
+      <c r="C366" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D366" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E366" t="str">
+        <v>Exaze It</v>
+      </c>
+      <c r="F366" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G366" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-exaze-it-hyderabad-7-to-15-years-030826501979</v>
+      </c>
+      <c r="H366" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-exaze-it-hyderabad-7-to-15-years-030826501979</v>
+      </c>
+      <c r="I366" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367" t="str">
+        <v>3/9/2026, 12:08:42 pm</v>
+      </c>
+      <c r="C367" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D367" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E367" t="str">
+        <v>Hoffmann La Roche</v>
+      </c>
+      <c r="F367" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G367" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-hoffmann-la-roche-hyderabad-1-to-5-years-200826501364</v>
+      </c>
+      <c r="H367" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-hoffmann-la-roche-hyderabad-1-to-5-years-200826501364</v>
+      </c>
+      <c r="I367" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368" t="str">
+        <v>3/9/2026, 12:09:01 pm</v>
+      </c>
+      <c r="C368" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D368" t="str">
+        <v>REACT DEVELOPER</v>
+      </c>
+      <c r="E368" t="str">
+        <v>Kofuku Idea Labs</v>
+      </c>
+      <c r="F368" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G368" t="str">
+        <v>https://www.naukri.com/job-listings-react-developer-kofuku-idea-labs-hyderabad-3-to-6-years-301122500006</v>
+      </c>
+      <c r="H368" t="str">
+        <v>https://www.naukri.com/job-listings-react-developer-kofuku-idea-labs-hyderabad-3-to-6-years-301122500006</v>
+      </c>
+      <c r="I368" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369" t="str">
+        <v>3/9/2026, 12:09:06 pm</v>
+      </c>
+      <c r="C369" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D369" t="str">
+        <v>React Developer</v>
+      </c>
+      <c r="E369" t="str">
+        <v>Midh Technologies</v>
+      </c>
+      <c r="F369" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G369" t="str">
+        <v>https://www.naukri.com/job-listings-react-developer-midhtechnologies-pvt-ltd-hyderabad-2-to-5-years-200326502462</v>
+      </c>
+      <c r="H369" t="str">
+        <v>https://www.naukri.com/job-listings-react-developer-midhtechnologies-pvt-ltd-hyderabad-2-to-5-years-200326502462</v>
+      </c>
+      <c r="I369" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I333"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I369"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10587,7 +12298,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I419"/>
+  <dimension ref="A1:I600"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -22751,9 +24462,5258 @@
         <v>unknown_state</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420">
+        <v>419</v>
+      </c>
+      <c r="B420" t="str">
+        <v>3/9/2026, 11:35:06 am</v>
+      </c>
+      <c r="C420" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D420" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E420" t="str">
+        <v>Virtuous Tech</v>
+      </c>
+      <c r="F420" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="G420" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-virtuous-tech-hyderabad-2-to-4-years-200826018107</v>
+      </c>
+      <c r="H420" t="str">
+        <v/>
+      </c>
+      <c r="I420" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421">
+        <v>420</v>
+      </c>
+      <c r="B421" t="str">
+        <v>3/9/2026, 11:35:15 am</v>
+      </c>
+      <c r="C421" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D421" t="str">
+        <v>Java Full Stack Developer(Angular/React)(2-3 years)</v>
+      </c>
+      <c r="E421" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F421" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G421" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-angular-react-2-3-years-infosys-hyderabad-chennai-bengaluru-2-to-3-years-030826024220</v>
+      </c>
+      <c r="H421" t="str">
+        <v/>
+      </c>
+      <c r="I421" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422">
+        <v>421</v>
+      </c>
+      <c r="B422" t="str">
+        <v>3/9/2026, 11:35:43 am</v>
+      </c>
+      <c r="C422" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D422" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E422" t="str">
+        <v>Tekskills</v>
+      </c>
+      <c r="F422" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G422" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-hyderabad-chennai-bengaluru-6-to-11-years-020926021060</v>
+      </c>
+      <c r="H422" t="str">
+        <v/>
+      </c>
+      <c r="I422" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423">
+        <v>422</v>
+      </c>
+      <c r="B423" t="str">
+        <v>3/9/2026, 11:36:21 am</v>
+      </c>
+      <c r="C423" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D423" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E423" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F423" t="str">
+        <v>Hybrid - Hyderabad, Pune, Chennai</v>
+      </c>
+      <c r="G423" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-pune-chennai-4-to-9-years-020926035005</v>
+      </c>
+      <c r="H423" t="str">
+        <v/>
+      </c>
+      <c r="I423" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424">
+        <v>423</v>
+      </c>
+      <c r="B424" t="str">
+        <v>3/9/2026, 11:36:29 am</v>
+      </c>
+      <c r="C424" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D424" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E424" t="str">
+        <v>Cloudxtreme</v>
+      </c>
+      <c r="F424" t="str">
+        <v>Hybrid - Hyderabad, Pune, Chennai</v>
+      </c>
+      <c r="G424" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cloudxtreme-hyderabad-pune-chennai-6-to-11-years-030926009784</v>
+      </c>
+      <c r="H424" t="str">
+        <v/>
+      </c>
+      <c r="I424" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425">
+        <v>424</v>
+      </c>
+      <c r="B425" t="str">
+        <v>3/9/2026, 11:36:46 am</v>
+      </c>
+      <c r="C425" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D425" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E425" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F425" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G425" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-bengaluru-5-to-9-years-020926030850</v>
+      </c>
+      <c r="H425" t="str">
+        <v/>
+      </c>
+      <c r="I425" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426">
+        <v>425</v>
+      </c>
+      <c r="B426" t="str">
+        <v>3/9/2026, 11:37:14 am</v>
+      </c>
+      <c r="C426" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D426" t="str">
+        <v>Urgent opening For Java Full Stack Developer</v>
+      </c>
+      <c r="E426" t="str">
+        <v>HCLTech</v>
+      </c>
+      <c r="F426" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G426" t="str">
+        <v>https://www.naukri.com/job-listings-urgent-opening-for-java-full-stack-developer-hcltech-hyderabad-chennai-bengaluru-8-to-13-years-020926034480</v>
+      </c>
+      <c r="H426" t="str">
+        <v/>
+      </c>
+      <c r="I426" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427">
+        <v>426</v>
+      </c>
+      <c r="B427" t="str">
+        <v>3/9/2026, 11:37:22 am</v>
+      </c>
+      <c r="C427" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D427" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E427" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F427" t="str">
+        <v>Hybrid - Hyderabad, Ahmedabad, Bengaluru</v>
+      </c>
+      <c r="G427" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-infosys-hyderabad-ahmedabad-bengaluru-10-to-20-years-020926032447</v>
+      </c>
+      <c r="H427" t="str">
+        <v/>
+      </c>
+      <c r="I427" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428">
+        <v>427</v>
+      </c>
+      <c r="B428" t="str">
+        <v>3/9/2026, 11:37:57 am</v>
+      </c>
+      <c r="C428" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D428" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E428" t="str">
+        <v>CGI</v>
+      </c>
+      <c r="F428" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G428" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-talent21-hyderabad-6-to-10-years-020926014653</v>
+      </c>
+      <c r="H428" t="str">
+        <v/>
+      </c>
+      <c r="I428" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429">
+        <v>428</v>
+      </c>
+      <c r="B429" t="str">
+        <v>3/9/2026, 11:38:09 am</v>
+      </c>
+      <c r="C429" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D429" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E429" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F429" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G429" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-infosys-hyderabad-chennai-bengaluru-9-to-14-years-010926026344</v>
+      </c>
+      <c r="H429" t="str">
+        <v/>
+      </c>
+      <c r="I429" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430">
+        <v>429</v>
+      </c>
+      <c r="B430" t="str">
+        <v>3/9/2026, 11:38:17 am</v>
+      </c>
+      <c r="C430" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D430" t="str">
+        <v>Java Full Stack Developer - Hyderabad</v>
+      </c>
+      <c r="E430" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F430" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G430" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-hyderabad-infosys-hyderabad-3-to-8-years-270426030941</v>
+      </c>
+      <c r="H430" t="str">
+        <v/>
+      </c>
+      <c r="I430" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431">
+        <v>430</v>
+      </c>
+      <c r="B431" t="str">
+        <v>3/9/2026, 11:38:30 am</v>
+      </c>
+      <c r="C431" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D431" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E431" t="str">
+        <v>Leuwint Technologies</v>
+      </c>
+      <c r="F431" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G431" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-leuwint-technologies-hyderabad-bengaluru-10-to-15-years-270826028074</v>
+      </c>
+      <c r="H431" t="str">
+        <v/>
+      </c>
+      <c r="I431" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432">
+        <v>431</v>
+      </c>
+      <c r="B432" t="str">
+        <v>3/9/2026, 11:38:57 am</v>
+      </c>
+      <c r="C432" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D432" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E432" t="str">
+        <v>Deloitte US-India Offices</v>
+      </c>
+      <c r="F432" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G432" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-deloitte-us-india-offices-hyderabad-9-to-12-years-270826023630</v>
+      </c>
+      <c r="H432" t="str">
+        <v/>
+      </c>
+      <c r="I432" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433">
+        <v>432</v>
+      </c>
+      <c r="B433" t="str">
+        <v>3/9/2026, 11:39:05 am</v>
+      </c>
+      <c r="C433" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D433" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E433" t="str">
+        <v>Tekskills</v>
+      </c>
+      <c r="F433" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G433" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-hyderabad-9-to-14-years-270826021773</v>
+      </c>
+      <c r="H433" t="str">
+        <v/>
+      </c>
+      <c r="I433" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434">
+        <v>433</v>
+      </c>
+      <c r="B434" t="str">
+        <v>3/9/2026, 11:39:35 am</v>
+      </c>
+      <c r="C434" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D434" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E434" t="str">
+        <v>CGI</v>
+      </c>
+      <c r="F434" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G434" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cgi-hyderabad-bengaluru-4-to-8-years-270826017278</v>
+      </c>
+      <c r="H434" t="str">
+        <v/>
+      </c>
+      <c r="I434" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435">
+        <v>434</v>
+      </c>
+      <c r="B435" t="str">
+        <v>3/9/2026, 11:39:43 am</v>
+      </c>
+      <c r="C435" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D435" t="str">
+        <v>Java Full Stack Developer- Infosys</v>
+      </c>
+      <c r="E435" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F435" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G435" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-infosys-infosys-hyderabad-5-to-9-years-060426029710</v>
+      </c>
+      <c r="H435" t="str">
+        <v/>
+      </c>
+      <c r="I435" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436">
+        <v>435</v>
+      </c>
+      <c r="B436" t="str">
+        <v>3/9/2026, 11:40:30 am</v>
+      </c>
+      <c r="C436" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D436" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E436" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F436" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G436" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-chennai-bengaluru-6-to-9-years-020926025753</v>
+      </c>
+      <c r="H436" t="str">
+        <v/>
+      </c>
+      <c r="I436" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437">
+        <v>436</v>
+      </c>
+      <c r="B437" t="str">
+        <v>3/9/2026, 11:40:38 am</v>
+      </c>
+      <c r="C437" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D437" t="str">
+        <v>AWS Java Full Stack Developer - Angular</v>
+      </c>
+      <c r="E437" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F437" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G437" t="str">
+        <v>https://www.naukri.com/job-listings-aws-java-full-stack-developer-angular-tata-consultancy-services-hyderabad-chennai-bengaluru-8-to-10-years-010926037494</v>
+      </c>
+      <c r="H437" t="str">
+        <v/>
+      </c>
+      <c r="I437" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438">
+        <v>437</v>
+      </c>
+      <c r="B438" t="str">
+        <v>3/9/2026, 11:40:46 am</v>
+      </c>
+      <c r="C438" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D438" t="str">
+        <v>Java Full Stack Developer(Java+React)</v>
+      </c>
+      <c r="E438" t="str">
+        <v>LTM</v>
+      </c>
+      <c r="F438" t="str">
+        <v>Hyderabad, Indore, Pune</v>
+      </c>
+      <c r="G438" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-java-react-alike-thoughts-indore-hyderabad-pune-7-to-12-years-010926035771</v>
+      </c>
+      <c r="H438" t="str">
+        <v/>
+      </c>
+      <c r="I438" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439">
+        <v>438</v>
+      </c>
+      <c r="B439" t="str">
+        <v>3/9/2026, 11:41:06 am</v>
+      </c>
+      <c r="C439" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D439" t="str">
+        <v>Java Full Stack Developer with AI</v>
+      </c>
+      <c r="E439" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F439" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G439" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-with-ai-capgemini-hyderabad-6-to-8-years-270826030300</v>
+      </c>
+      <c r="H439" t="str">
+        <v/>
+      </c>
+      <c r="I439" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440">
+        <v>439</v>
+      </c>
+      <c r="B440" t="str">
+        <v>3/9/2026, 11:42:00 am</v>
+      </c>
+      <c r="C440" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D440" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E440" t="str">
+        <v>Techwise Digital</v>
+      </c>
+      <c r="F440" t="str">
+        <v>Hyderabad, Noida, Bengaluru</v>
+      </c>
+      <c r="G440" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-indihire-consultants-noida-hyderabad-bengaluru-8-to-13-years-210826014629</v>
+      </c>
+      <c r="H440" t="str">
+        <v/>
+      </c>
+      <c r="I440" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441">
+        <v>440</v>
+      </c>
+      <c r="B441" t="str">
+        <v>3/9/2026, 11:42:08 am</v>
+      </c>
+      <c r="C441" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D441" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E441" t="str">
+        <v>WSNE Consulting</v>
+      </c>
+      <c r="F441" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G441" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-wsne-consulting-hyderabad-7-to-12-years-200826035608</v>
+      </c>
+      <c r="H441" t="str">
+        <v/>
+      </c>
+      <c r="I441" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442">
+        <v>441</v>
+      </c>
+      <c r="B442" t="str">
+        <v>3/9/2026, 11:42:36 am</v>
+      </c>
+      <c r="C442" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D442" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E442" t="str">
+        <v>SRS Infoway</v>
+      </c>
+      <c r="F442" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G442" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-srs-infoway-hyderabad-pune-bengaluru-5-to-10-years-090726008564</v>
+      </c>
+      <c r="H442" t="str">
+        <v/>
+      </c>
+      <c r="I442" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443">
+        <v>442</v>
+      </c>
+      <c r="B443" t="str">
+        <v>3/9/2026, 11:43:06 am</v>
+      </c>
+      <c r="C443" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D443" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E443" t="str">
+        <v>Cloudxtreme</v>
+      </c>
+      <c r="F443" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G443" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cloudxtreme-hyderabad-chennai-bengaluru-4-to-9-years-010826006559</v>
+      </c>
+      <c r="H443" t="str">
+        <v/>
+      </c>
+      <c r="I443" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444">
+        <v>443</v>
+      </c>
+      <c r="B444" t="str">
+        <v>3/9/2026, 11:43:14 am</v>
+      </c>
+      <c r="C444" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D444" t="str">
+        <v>Java Full Stack Developer + Agentic AI</v>
+      </c>
+      <c r="E444" t="str">
+        <v>Cognizant</v>
+      </c>
+      <c r="F444" t="str">
+        <v>Hybrid - Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G444" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-agentic-ai-cognizant-hyderabad-bengaluru-10-to-15-years-280726006393</v>
+      </c>
+      <c r="H444" t="str">
+        <v/>
+      </c>
+      <c r="I444" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445">
+        <v>444</v>
+      </c>
+      <c r="B445" t="str">
+        <v>3/9/2026, 11:43:22 am</v>
+      </c>
+      <c r="C445" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D445" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E445" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F445" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G445" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tata-consultancy-services-hyderabad-6-to-9-years-220826009856</v>
+      </c>
+      <c r="H445" t="str">
+        <v/>
+      </c>
+      <c r="I445" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446">
+        <v>445</v>
+      </c>
+      <c r="B446" t="str">
+        <v>3/9/2026, 11:43:34 am</v>
+      </c>
+      <c r="C446" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D446" t="str">
+        <v>Senior Java Full Stack Developer ( Java + React )</v>
+      </c>
+      <c r="E446" t="str">
+        <v>Sdkm Solutions</v>
+      </c>
+      <c r="F446" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G446" t="str">
+        <v>https://www.naukri.com/job-listings-senior-java-full-stack-developer-java-react-sdkm-solutions-hyderabad-8-to-13-years-020926019722</v>
+      </c>
+      <c r="H446" t="str">
+        <v/>
+      </c>
+      <c r="I446" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447">
+        <v>446</v>
+      </c>
+      <c r="B447" t="str">
+        <v>3/9/2026, 11:44:19 am</v>
+      </c>
+      <c r="C447" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D447" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E447" t="str">
+        <v>Vbeyond Corporation</v>
+      </c>
+      <c r="F447" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G447" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-vbeyond-corporation-hyderabad-5-to-8-years-250826014397</v>
+      </c>
+      <c r="H447" t="str">
+        <v/>
+      </c>
+      <c r="I447" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448">
+        <v>447</v>
+      </c>
+      <c r="B448" t="str">
+        <v>3/9/2026, 11:44:27 am</v>
+      </c>
+      <c r="C448" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D448" t="str">
+        <v>Lead Java Full-Stack Developer (Angular)</v>
+      </c>
+      <c r="E448" t="str">
+        <v>Epam Systems</v>
+      </c>
+      <c r="F448" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G448" t="str">
+        <v>https://www.naukri.com/job-listings-lead-java-full-stack-developer-angular-epam-systems-hyderabad-10-to-14-years-240826007061</v>
+      </c>
+      <c r="H448" t="str">
+        <v/>
+      </c>
+      <c r="I448" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449">
+        <v>448</v>
+      </c>
+      <c r="B449" t="str">
+        <v>3/9/2026, 11:44:35 am</v>
+      </c>
+      <c r="C449" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D449" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E449" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F449" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G449" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-private-limited-hyderabad-8-to-13-years-210826916881</v>
+      </c>
+      <c r="H449" t="str">
+        <v/>
+      </c>
+      <c r="I449" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450">
+        <v>449</v>
+      </c>
+      <c r="B450" t="str">
+        <v>3/9/2026, 11:44:43 am</v>
+      </c>
+      <c r="C450" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D450" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E450" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F450" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G450" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-private-limited-hyderabad-5-to-10-years-210826916806</v>
+      </c>
+      <c r="H450" t="str">
+        <v/>
+      </c>
+      <c r="I450" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451">
+        <v>450</v>
+      </c>
+      <c r="B451" t="str">
+        <v>3/9/2026, 11:44:51 am</v>
+      </c>
+      <c r="C451" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D451" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E451" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F451" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G451" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-private-limited-hyderabad-5-to-10-years-210826910752</v>
+      </c>
+      <c r="H451" t="str">
+        <v/>
+      </c>
+      <c r="I451" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452">
+        <v>451</v>
+      </c>
+      <c r="B452" t="str">
+        <v>3/9/2026, 11:45:07 am</v>
+      </c>
+      <c r="C452" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D452" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E452" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F452" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G452" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-private-limited-hyderabad-6-to-10-years-200826928321</v>
+      </c>
+      <c r="H452" t="str">
+        <v/>
+      </c>
+      <c r="I452" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453">
+        <v>452</v>
+      </c>
+      <c r="B453" t="str">
+        <v>3/9/2026, 11:45:15 am</v>
+      </c>
+      <c r="C453" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D453" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E453" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F453" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G453" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-private-limited-hyderabad-6-to-11-years-200826928249</v>
+      </c>
+      <c r="H453" t="str">
+        <v/>
+      </c>
+      <c r="I453" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454">
+        <v>453</v>
+      </c>
+      <c r="B454" t="str">
+        <v>3/9/2026, 11:45:23 am</v>
+      </c>
+      <c r="C454" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D454" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E454" t="str">
+        <v>Pineq Technology Labs</v>
+      </c>
+      <c r="F454" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G454" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-pineq-technology-labs-hyderabad-chennai-bengaluru-8-to-11-years-200826034027</v>
+      </c>
+      <c r="H454" t="str">
+        <v/>
+      </c>
+      <c r="I454" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455">
+        <v>454</v>
+      </c>
+      <c r="B455" t="str">
+        <v>3/9/2026, 11:45:56 am</v>
+      </c>
+      <c r="C455" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D455" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E455" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F455" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G455" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-infosys-limited-hyderabad-5-to-9-years-170826920003</v>
+      </c>
+      <c r="H455" t="str">
+        <v/>
+      </c>
+      <c r="I455" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456">
+        <v>455</v>
+      </c>
+      <c r="B456" t="str">
+        <v>3/9/2026, 11:46:23 am</v>
+      </c>
+      <c r="C456" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D456" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E456" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F456" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G456" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-infosys-hyderabad-5-to-9-years-270426028951</v>
+      </c>
+      <c r="H456" t="str">
+        <v/>
+      </c>
+      <c r="I456" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457">
+        <v>456</v>
+      </c>
+      <c r="B457" t="str">
+        <v>3/9/2026, 11:46:43 am</v>
+      </c>
+      <c r="C457" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D457" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E457" t="str">
+        <v>Quess Corp Limited</v>
+      </c>
+      <c r="F457" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G457" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-quess-hyderabad-bengaluru-6-to-9-years-260826013701</v>
+      </c>
+      <c r="H457" t="str">
+        <v/>
+      </c>
+      <c r="I457" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458">
+        <v>457</v>
+      </c>
+      <c r="B458" t="str">
+        <v>3/9/2026, 11:46:59 am</v>
+      </c>
+      <c r="C458" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D458" t="str">
+        <v>Java Full Stack Developer -N</v>
+      </c>
+      <c r="E458" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F458" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G458" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-n-tata-consultancy-services-hyderabad-chennai-bengaluru-5-to-8-years-250826029028</v>
+      </c>
+      <c r="H458" t="str">
+        <v/>
+      </c>
+      <c r="I458" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459">
+        <v>458</v>
+      </c>
+      <c r="B459" t="str">
+        <v>3/9/2026, 11:47:14 am</v>
+      </c>
+      <c r="C459" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D459" t="str">
+        <v>Java Full Stack Developer - Java MSB + Angular</v>
+      </c>
+      <c r="E459" t="str">
+        <v>Cognizant</v>
+      </c>
+      <c r="F459" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G459" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-java-msb-angular-cognizant-hyderabad-10-to-14-years-190826017433</v>
+      </c>
+      <c r="H459" t="str">
+        <v/>
+      </c>
+      <c r="I459" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460">
+        <v>459</v>
+      </c>
+      <c r="B460" t="str">
+        <v>3/9/2026, 11:47:22 am</v>
+      </c>
+      <c r="C460" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D460" t="str">
+        <v>Java Full Stack Developer - Java MSB + Angular</v>
+      </c>
+      <c r="E460" t="str">
+        <v>Cognizant</v>
+      </c>
+      <c r="F460" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G460" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-java-msb-angular-cognizant-hyderabad-6-to-9-years-190826017364</v>
+      </c>
+      <c r="H460" t="str">
+        <v/>
+      </c>
+      <c r="I460" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461">
+        <v>460</v>
+      </c>
+      <c r="B461" t="str">
+        <v>3/9/2026, 11:47:31 am</v>
+      </c>
+      <c r="C461" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D461" t="str">
+        <v>Java Full Stack Developer (Java + React)</v>
+      </c>
+      <c r="E461" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F461" t="str">
+        <v>Hybrid - Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G461" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-java-react-capgemini-hyderabad-pune-bengaluru-6-to-8-years-160726018294</v>
+      </c>
+      <c r="H461" t="str">
+        <v/>
+      </c>
+      <c r="I461" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462">
+        <v>461</v>
+      </c>
+      <c r="B462" t="str">
+        <v>3/9/2026, 11:48:08 am</v>
+      </c>
+      <c r="C462" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D462" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E462" t="str">
+        <v>IT Industry</v>
+      </c>
+      <c r="F462" t="str">
+        <v>Hyderabad, Bengaluru, Delhi / NCR</v>
+      </c>
+      <c r="G462" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-serendipity-corporate-services-hyderabad-bengaluru-delhi-ncr-5-to-9-years-120826919713</v>
+      </c>
+      <c r="H462" t="str">
+        <v/>
+      </c>
+      <c r="I462" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463">
+        <v>462</v>
+      </c>
+      <c r="B463" t="str">
+        <v>3/9/2026, 11:48:43 am</v>
+      </c>
+      <c r="C463" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D463" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E463" t="str">
+        <v>Valuelabs</v>
+      </c>
+      <c r="F463" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G463" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-valuelabs-hyderabad-6-to-11-years-100826023325</v>
+      </c>
+      <c r="H463" t="str">
+        <v/>
+      </c>
+      <c r="I463" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464">
+        <v>463</v>
+      </c>
+      <c r="B464" t="str">
+        <v>3/9/2026, 11:48:51 am</v>
+      </c>
+      <c r="C464" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D464" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E464" t="str">
+        <v>Valuelabs</v>
+      </c>
+      <c r="F464" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G464" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-valuelabs-hyderabad-5-to-10-years-100826020952</v>
+      </c>
+      <c r="H464" t="str">
+        <v/>
+      </c>
+      <c r="I464" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465">
+        <v>464</v>
+      </c>
+      <c r="B465" t="str">
+        <v>3/9/2026, 11:49:07 am</v>
+      </c>
+      <c r="C465" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D465" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E465" t="str">
+        <v>Evoke Technologies</v>
+      </c>
+      <c r="F465" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G465" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-evoke-technologies-hyderabad-7-to-12-years-040826032441</v>
+      </c>
+      <c r="H465" t="str">
+        <v/>
+      </c>
+      <c r="I465" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466">
+        <v>465</v>
+      </c>
+      <c r="B466" t="str">
+        <v>3/9/2026, 11:49:43 am</v>
+      </c>
+      <c r="C466" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D466" t="str">
+        <v>Java Full Stack Developer @ Pan India</v>
+      </c>
+      <c r="E466" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F466" t="str">
+        <v>Hyderabad, Bengaluru, Delhi / NCR</v>
+      </c>
+      <c r="G466" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-pan-india-infosys-hyderabad-bengaluru-delhi-ncr-5-to-8-years-270426033372</v>
+      </c>
+      <c r="H466" t="str">
+        <v/>
+      </c>
+      <c r="I466" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467">
+        <v>466</v>
+      </c>
+      <c r="B467" t="str">
+        <v>3/9/2026, 11:49:51 am</v>
+      </c>
+      <c r="C467" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D467" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E467" t="str">
+        <v>CGI</v>
+      </c>
+      <c r="F467" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G467" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cgi-hyderabad-5-to-9-years-260826022501</v>
+      </c>
+      <c r="H467" t="str">
+        <v/>
+      </c>
+      <c r="I467" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468">
+        <v>467</v>
+      </c>
+      <c r="B468" t="str">
+        <v>3/9/2026, 11:49:59 am</v>
+      </c>
+      <c r="C468" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D468" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E468" t="str">
+        <v>Teamware Solutions</v>
+      </c>
+      <c r="F468" t="str">
+        <v>Hyderabad, Noida, Bengaluru</v>
+      </c>
+      <c r="G468" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-teamware-solutions-noida-hyderabad-bengaluru-8-to-15-years-250826018894</v>
+      </c>
+      <c r="H468" t="str">
+        <v/>
+      </c>
+      <c r="I468" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469">
+        <v>468</v>
+      </c>
+      <c r="B469" t="str">
+        <v>3/9/2026, 11:50:07 am</v>
+      </c>
+      <c r="C469" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D469" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E469" t="str">
+        <v>Value Spectrum Technologies</v>
+      </c>
+      <c r="F469" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G469" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-value-spectrum-technologies-hyderabad-5-to-10-years-250826013231</v>
+      </c>
+      <c r="H469" t="str">
+        <v/>
+      </c>
+      <c r="I469" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470">
+        <v>469</v>
+      </c>
+      <c r="B470" t="str">
+        <v>3/9/2026, 11:50:15 am</v>
+      </c>
+      <c r="C470" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D470" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E470" t="str">
+        <v>CGI</v>
+      </c>
+      <c r="F470" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G470" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cgi-hyderabad-7-to-9-years-210826030559</v>
+      </c>
+      <c r="H470" t="str">
+        <v/>
+      </c>
+      <c r="I470" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471">
+        <v>470</v>
+      </c>
+      <c r="B471" t="str">
+        <v>3/9/2026, 11:50:23 am</v>
+      </c>
+      <c r="C471" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D471" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E471" t="str">
+        <v>Rekrut India</v>
+      </c>
+      <c r="F471" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G471" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-rekrut-india-hyderabad-chennai-bengaluru-5-to-8-years-190826025514</v>
+      </c>
+      <c r="H471" t="str">
+        <v/>
+      </c>
+      <c r="I471" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472">
+        <v>471</v>
+      </c>
+      <c r="B472" t="str">
+        <v>3/9/2026, 11:50:31 am</v>
+      </c>
+      <c r="C472" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D472" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E472" t="str">
+        <v>Lloyds Technology Centre</v>
+      </c>
+      <c r="F472" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G472" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-lloyds-technology-centre-hyderabad-8-to-13-years-190826017882</v>
+      </c>
+      <c r="H472" t="str">
+        <v/>
+      </c>
+      <c r="I472" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473">
+        <v>472</v>
+      </c>
+      <c r="B473" t="str">
+        <v>3/9/2026, 11:50:39 am</v>
+      </c>
+      <c r="C473" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D473" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E473" t="str">
+        <v>IonIdea</v>
+      </c>
+      <c r="F473" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G473" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-ionidea-hyderabad-pune-bengaluru-4-to-6-years-190826010997</v>
+      </c>
+      <c r="H473" t="str">
+        <v/>
+      </c>
+      <c r="I473" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474">
+        <v>473</v>
+      </c>
+      <c r="B474" t="str">
+        <v>3/9/2026, 11:50:47 am</v>
+      </c>
+      <c r="C474" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D474" t="str">
+        <v>Java Full Stack Developer-Hyderabad (5-9 yrs)</v>
+      </c>
+      <c r="E474" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F474" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G474" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-hyderabad-5-9-yrs-infosys-hyderabad-5-to-9-years-050626026128</v>
+      </c>
+      <c r="H474" t="str">
+        <v/>
+      </c>
+      <c r="I474" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475">
+        <v>474</v>
+      </c>
+      <c r="B475" t="str">
+        <v>3/9/2026, 11:50:55 am</v>
+      </c>
+      <c r="C475" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D475" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E475" t="str">
+        <v>Tech Mahindra</v>
+      </c>
+      <c r="F475" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G475" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tech-mahindra-hyderabad-5-to-8-years-240826025995</v>
+      </c>
+      <c r="H475" t="str">
+        <v/>
+      </c>
+      <c r="I475" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476">
+        <v>475</v>
+      </c>
+      <c r="B476" t="str">
+        <v>3/9/2026, 11:51:03 am</v>
+      </c>
+      <c r="C476" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D476" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E476" t="str">
+        <v>Hexaware Technologies</v>
+      </c>
+      <c r="F476" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G476" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-hexaware-technologies-hyderabad-chennai-bengaluru-6-to-10-years-290626001311</v>
+      </c>
+      <c r="H476" t="str">
+        <v/>
+      </c>
+      <c r="I476" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477">
+        <v>476</v>
+      </c>
+      <c r="B477" t="str">
+        <v>3/9/2026, 11:51:11 am</v>
+      </c>
+      <c r="C477" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D477" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E477" t="str">
+        <v>Akshaya Business It Solutions</v>
+      </c>
+      <c r="F477" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G477" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-akshaya-business-it-solutions-hyderabad-5-to-10-years-240826014323</v>
+      </c>
+      <c r="H477" t="str">
+        <v/>
+      </c>
+      <c r="I477" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478">
+        <v>477</v>
+      </c>
+      <c r="B478" t="str">
+        <v>3/9/2026, 11:51:19 am</v>
+      </c>
+      <c r="C478" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D478" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E478" t="str">
+        <v>Cloudxtreme</v>
+      </c>
+      <c r="F478" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G478" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cloudxtreme-hyderabad-chennai-bengaluru-4-to-6-years-210726007196</v>
+      </c>
+      <c r="H478" t="str">
+        <v/>
+      </c>
+      <c r="I478" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479">
+        <v>478</v>
+      </c>
+      <c r="B479" t="str">
+        <v>3/9/2026, 11:51:27 am</v>
+      </c>
+      <c r="C479" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D479" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E479" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F479" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G479" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-private-limited-hyderabad-5-to-10-years-180826930849</v>
+      </c>
+      <c r="H479" t="str">
+        <v/>
+      </c>
+      <c r="I479" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480">
+        <v>479</v>
+      </c>
+      <c r="B480" t="str">
+        <v>3/9/2026, 11:51:35 am</v>
+      </c>
+      <c r="C480" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D480" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E480" t="str">
+        <v>LTM</v>
+      </c>
+      <c r="F480" t="str">
+        <v>Hybrid - Hyderabad, Chennai</v>
+      </c>
+      <c r="G480" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-ltm-hyderabad-chennai-6-to-8-years-170826010066</v>
+      </c>
+      <c r="H480" t="str">
+        <v/>
+      </c>
+      <c r="I480" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481">
+        <v>480</v>
+      </c>
+      <c r="B481" t="str">
+        <v>3/9/2026, 11:51:43 am</v>
+      </c>
+      <c r="C481" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D481" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E481" t="str">
+        <v>Hexaware Technologies</v>
+      </c>
+      <c r="F481" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G481" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-hexaware-technologies-hyderabad-chennai-bengaluru-9-to-12-years-170826006105</v>
+      </c>
+      <c r="H481" t="str">
+        <v/>
+      </c>
+      <c r="I481" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482">
+        <v>481</v>
+      </c>
+      <c r="B482" t="str">
+        <v>3/9/2026, 11:51:51 am</v>
+      </c>
+      <c r="C482" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D482" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E482" t="str">
+        <v>CGI</v>
+      </c>
+      <c r="F482" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G482" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cgi-hyderabad-6-to-9-years-120826033057</v>
+      </c>
+      <c r="H482" t="str">
+        <v/>
+      </c>
+      <c r="I482" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483">
+        <v>482</v>
+      </c>
+      <c r="B483" t="str">
+        <v>3/9/2026, 11:51:59 am</v>
+      </c>
+      <c r="C483" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D483" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E483" t="str">
+        <v>Nxtwave Disruptive Technologies (Hiring for a client)</v>
+      </c>
+      <c r="F483" t="str">
+        <v>Hyderabad, Indore, Ahmedabad</v>
+      </c>
+      <c r="G483" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-nxtwave-disruptive-technologies-hiring-for-a-client-indore-hyderabad-ahmedabad-5-to-9-years-070826039572</v>
+      </c>
+      <c r="H483" t="str">
+        <v/>
+      </c>
+      <c r="I483" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484">
+        <v>483</v>
+      </c>
+      <c r="B484" t="str">
+        <v>3/9/2026, 11:52:07 am</v>
+      </c>
+      <c r="C484" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D484" t="str">
+        <v>Java Full Stack Developer with Angular</v>
+      </c>
+      <c r="E484" t="str">
+        <v>Virtusa</v>
+      </c>
+      <c r="F484" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G484" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-with-angular-virtusa-hyderabad-pune-bengaluru-5-to-12-years-070826038214</v>
+      </c>
+      <c r="H484" t="str">
+        <v/>
+      </c>
+      <c r="I484" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485">
+        <v>484</v>
+      </c>
+      <c r="B485" t="str">
+        <v>3/9/2026, 11:52:15 am</v>
+      </c>
+      <c r="C485" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D485" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E485" t="str">
+        <v>Vbeyond Corporation</v>
+      </c>
+      <c r="F485" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G485" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-vbeyond-corporation-hyderabad-chennai-bengaluru-6-to-11-years-070826017108</v>
+      </c>
+      <c r="H485" t="str">
+        <v/>
+      </c>
+      <c r="I485" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486">
+        <v>485</v>
+      </c>
+      <c r="B486" t="str">
+        <v>3/9/2026, 11:52:24 am</v>
+      </c>
+      <c r="C486" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D486" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E486" t="str">
+        <v>Synechron</v>
+      </c>
+      <c r="F486" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G486" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-synechron-hyderabad-bengaluru-6-to-11-years-050826022946</v>
+      </c>
+      <c r="H486" t="str">
+        <v/>
+      </c>
+      <c r="I486" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487">
+        <v>486</v>
+      </c>
+      <c r="B487" t="str">
+        <v>3/9/2026, 11:52:31 am</v>
+      </c>
+      <c r="C487" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D487" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E487" t="str">
+        <v>Synechron</v>
+      </c>
+      <c r="F487" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G487" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-synechron-hyderabad-bengaluru-6-to-10-years-040826016978</v>
+      </c>
+      <c r="H487" t="str">
+        <v/>
+      </c>
+      <c r="I487" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488">
+        <v>487</v>
+      </c>
+      <c r="B488" t="str">
+        <v>3/9/2026, 11:52:39 am</v>
+      </c>
+      <c r="C488" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D488" t="str">
+        <v>Vue &amp; Java Full Stack Developer</v>
+      </c>
+      <c r="E488" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F488" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="G488" t="str">
+        <v>https://www.naukri.com/job-listings-vue-java-full-stack-developer-basebiz-hyderabad-9-to-12-years-030826918198</v>
+      </c>
+      <c r="H488" t="str">
+        <v/>
+      </c>
+      <c r="I488" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489">
+        <v>488</v>
+      </c>
+      <c r="B489" t="str">
+        <v>3/9/2026, 11:52:47 am</v>
+      </c>
+      <c r="C489" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D489" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E489" t="str">
+        <v>TekWissen</v>
+      </c>
+      <c r="F489" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G489" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekwissen-hyderabad-6-to-11-years-030826022053</v>
+      </c>
+      <c r="H489" t="str">
+        <v/>
+      </c>
+      <c r="I489" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490">
+        <v>489</v>
+      </c>
+      <c r="B490" t="str">
+        <v>3/9/2026, 11:52:56 am</v>
+      </c>
+      <c r="C490" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D490" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E490" t="str">
+        <v>CGI</v>
+      </c>
+      <c r="F490" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G490" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cgi-hyderabad-6-to-10-years-030826016442</v>
+      </c>
+      <c r="H490" t="str">
+        <v/>
+      </c>
+      <c r="I490" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491">
+        <v>490</v>
+      </c>
+      <c r="B491" t="str">
+        <v>3/9/2026, 11:53:04 am</v>
+      </c>
+      <c r="C491" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D491" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E491" t="str">
+        <v>JPMorgan Chase Bank</v>
+      </c>
+      <c r="F491" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G491" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-sunovaa-tech-hyderabad-5-to-8-years-030826007925</v>
+      </c>
+      <c r="H491" t="str">
+        <v/>
+      </c>
+      <c r="I491" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492">
+        <v>491</v>
+      </c>
+      <c r="B492" t="str">
+        <v>3/9/2026, 11:53:12 am</v>
+      </c>
+      <c r="C492" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D492" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E492" t="str">
+        <v>The Hartford</v>
+      </c>
+      <c r="F492" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G492" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-the-hartford-hyderabad-6-to-14-years-020826004841</v>
+      </c>
+      <c r="H492" t="str">
+        <v/>
+      </c>
+      <c r="I492" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493">
+        <v>492</v>
+      </c>
+      <c r="B493" t="str">
+        <v>3/9/2026, 11:53:20 am</v>
+      </c>
+      <c r="C493" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D493" t="str">
+        <v>Java Full Stack Developer- Hyderabad</v>
+      </c>
+      <c r="E493" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F493" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G493" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-hyderabad-infosys-hyderabad-chennai-bengaluru-5-to-10-years-230726033383</v>
+      </c>
+      <c r="H493" t="str">
+        <v/>
+      </c>
+      <c r="I493" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494">
+        <v>493</v>
+      </c>
+      <c r="B494" t="str">
+        <v>3/9/2026, 11:53:28 am</v>
+      </c>
+      <c r="C494" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D494" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E494" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F494" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G494" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-pune-bengaluru-6-to-9-years-180826046379</v>
+      </c>
+      <c r="H494" t="str">
+        <v/>
+      </c>
+      <c r="I494" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495">
+        <v>494</v>
+      </c>
+      <c r="B495" t="str">
+        <v>3/9/2026, 11:53:36 am</v>
+      </c>
+      <c r="C495" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D495" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E495" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F495" t="str">
+        <v>Hybrid - Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G495" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-pune-bengaluru-4-to-9-years-180826036388</v>
+      </c>
+      <c r="H495" t="str">
+        <v/>
+      </c>
+      <c r="I495" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496">
+        <v>495</v>
+      </c>
+      <c r="B496" t="str">
+        <v>3/9/2026, 11:53:44 am</v>
+      </c>
+      <c r="C496" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D496" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E496" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F496" t="str">
+        <v>Hybrid - Hyderabad, Pune, Chennai</v>
+      </c>
+      <c r="G496" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-pune-chennai-6-to-9-years-180826036188</v>
+      </c>
+      <c r="H496" t="str">
+        <v/>
+      </c>
+      <c r="I496" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497">
+        <v>496</v>
+      </c>
+      <c r="B497" t="str">
+        <v>3/9/2026, 11:53:52 am</v>
+      </c>
+      <c r="C497" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D497" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E497" t="str">
+        <v>Vbeyond Corporation</v>
+      </c>
+      <c r="F497" t="str">
+        <v>Hybrid - Hyderabad, Noida</v>
+      </c>
+      <c r="G497" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-vbeyond-corporation-noida-hyderabad-7-to-12-years-180826010880</v>
+      </c>
+      <c r="H497" t="str">
+        <v/>
+      </c>
+      <c r="I497" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498">
+        <v>497</v>
+      </c>
+      <c r="B498" t="str">
+        <v>3/9/2026, 11:54:00 am</v>
+      </c>
+      <c r="C498" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D498" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E498" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F498" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G498" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tata-consultancy-services-hyderabad-chennai-bengaluru-4-to-9-years-180526023600</v>
+      </c>
+      <c r="H498" t="str">
+        <v/>
+      </c>
+      <c r="I498" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499">
+        <v>498</v>
+      </c>
+      <c r="B499" t="str">
+        <v>3/9/2026, 11:54:08 am</v>
+      </c>
+      <c r="C499" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D499" t="str">
+        <v>Java Full Stack Developer with React.js</v>
+      </c>
+      <c r="E499" t="str">
+        <v>Tech Mahindra</v>
+      </c>
+      <c r="F499" t="str">
+        <v>Hybrid - Hyderabad, Chennai</v>
+      </c>
+      <c r="G499" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-with-react-js-tech-mahindra-hyderabad-chennai-6-to-10-years-120826033567</v>
+      </c>
+      <c r="H499" t="str">
+        <v/>
+      </c>
+      <c r="I499" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500">
+        <v>499</v>
+      </c>
+      <c r="B500" t="str">
+        <v>3/9/2026, 11:54:16 am</v>
+      </c>
+      <c r="C500" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D500" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E500" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F500" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G500" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tata-consultancy-services-hyderabad-chennai-bengaluru-5-to-8-years-110826014643</v>
+      </c>
+      <c r="H500" t="str">
+        <v/>
+      </c>
+      <c r="I500" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501">
+        <v>500</v>
+      </c>
+      <c r="B501" t="str">
+        <v>3/9/2026, 11:54:24 am</v>
+      </c>
+      <c r="C501" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D501" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E501" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F501" t="str">
+        <v>Hyderabad, Pune, Chennai</v>
+      </c>
+      <c r="G501" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tata-consultancy-services-hyderabad-pune-chennai-6-to-10-years-100826010787</v>
+      </c>
+      <c r="H501" t="str">
+        <v/>
+      </c>
+      <c r="I501" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502">
+        <v>501</v>
+      </c>
+      <c r="B502" t="str">
+        <v>3/9/2026, 11:54:32 am</v>
+      </c>
+      <c r="C502" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D502" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E502" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F502" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G502" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tata-consultancy-services-hyderabad-chennai-bengaluru-4-to-9-years-100626035138</v>
+      </c>
+      <c r="H502" t="str">
+        <v/>
+      </c>
+      <c r="I502" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503">
+        <v>502</v>
+      </c>
+      <c r="B503" t="str">
+        <v>3/9/2026, 11:54:40 am</v>
+      </c>
+      <c r="C503" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D503" t="str">
+        <v>Java Full Stack Developer(angular)</v>
+      </c>
+      <c r="E503" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F503" t="str">
+        <v>Hybrid - Hyderabad, Ahmedabad, Bengaluru</v>
+      </c>
+      <c r="G503" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-angular-infosys-hyderabad-ahmedabad-bengaluru-5-to-9-years-060326031817</v>
+      </c>
+      <c r="H503" t="str">
+        <v/>
+      </c>
+      <c r="I503" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504">
+        <v>503</v>
+      </c>
+      <c r="B504" t="str">
+        <v>3/9/2026, 11:54:52 am</v>
+      </c>
+      <c r="C504" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D504" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E504" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F504" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G504" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-infosys-hyderabad-5-to-9-years-050526029661</v>
+      </c>
+      <c r="H504" t="str">
+        <v/>
+      </c>
+      <c r="I504" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505">
+        <v>504</v>
+      </c>
+      <c r="B505" t="str">
+        <v>3/9/2026, 11:55:04 am</v>
+      </c>
+      <c r="C505" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D505" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E505" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F505" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G505" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tata-consultancy-services-hyderabad-pune-bengaluru-7-to-12-years-030826022907</v>
+      </c>
+      <c r="H505" t="str">
+        <v/>
+      </c>
+      <c r="I505" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506">
+        <v>505</v>
+      </c>
+      <c r="B506" t="str">
+        <v>3/9/2026, 11:55:16 am</v>
+      </c>
+      <c r="C506" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D506" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E506" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F506" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G506" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-private-limited-hyderabad-7-to-12-years-210826912401</v>
+      </c>
+      <c r="H506" t="str">
+        <v/>
+      </c>
+      <c r="I506" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507">
+        <v>506</v>
+      </c>
+      <c r="B507" t="str">
+        <v>3/9/2026, 11:55:24 am</v>
+      </c>
+      <c r="C507" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D507" t="str">
+        <v>Senior Java Full-Stack Developer (Angular)</v>
+      </c>
+      <c r="E507" t="str">
+        <v>Epam Systems</v>
+      </c>
+      <c r="F507" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G507" t="str">
+        <v>https://www.naukri.com/job-listings-senior-java-full-stack-developer-angular-epam-systems-hyderabad-5-to-10-years-240826006920</v>
+      </c>
+      <c r="H507" t="str">
+        <v/>
+      </c>
+      <c r="I507" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508">
+        <v>507</v>
+      </c>
+      <c r="B508" t="str">
+        <v>3/9/2026, 11:55:32 am</v>
+      </c>
+      <c r="C508" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D508" t="str">
+        <v>Lead Java full stack developer</v>
+      </c>
+      <c r="E508" t="str">
+        <v>SM It Services</v>
+      </c>
+      <c r="F508" t="str">
+        <v>Hyderabad(Begumpet)</v>
+      </c>
+      <c r="G508" t="str">
+        <v>https://www.naukri.com/job-listings-lead-java-full-stack-developer-sm-it-services-hyderabad-10-to-15-years-050826020654</v>
+      </c>
+      <c r="H508" t="str">
+        <v/>
+      </c>
+      <c r="I508" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509">
+        <v>508</v>
+      </c>
+      <c r="B509" t="str">
+        <v>3/9/2026, 11:55:49 am</v>
+      </c>
+      <c r="C509" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D509" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E509" t="str">
+        <v>Tekskills</v>
+      </c>
+      <c r="F509" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G509" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-hyderabad-6-to-8-years-180826940562</v>
+      </c>
+      <c r="H509" t="str">
+        <v/>
+      </c>
+      <c r="I509" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510">
+        <v>509</v>
+      </c>
+      <c r="B510" t="str">
+        <v>3/9/2026, 11:55:57 am</v>
+      </c>
+      <c r="C510" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D510" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E510" t="str">
+        <v>Tekskills india</v>
+      </c>
+      <c r="F510" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G510" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-hyderabad-7-to-10-years-180826938800</v>
+      </c>
+      <c r="H510" t="str">
+        <v/>
+      </c>
+      <c r="I510" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511">
+        <v>510</v>
+      </c>
+      <c r="B511" t="str">
+        <v>3/9/2026, 11:56:05 am</v>
+      </c>
+      <c r="C511" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D511" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E511" t="str">
+        <v>Tekskills</v>
+      </c>
+      <c r="F511" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G511" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-hyderabad-6-to-10-years-180826938326</v>
+      </c>
+      <c r="H511" t="str">
+        <v/>
+      </c>
+      <c r="I511" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512">
+        <v>511</v>
+      </c>
+      <c r="B512" t="str">
+        <v>3/9/2026, 11:56:13 am</v>
+      </c>
+      <c r="C512" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D512" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E512" t="str">
+        <v>Tekskills India</v>
+      </c>
+      <c r="F512" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G512" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-hyderabad-8-to-13-years-180826934476</v>
+      </c>
+      <c r="H512" t="str">
+        <v/>
+      </c>
+      <c r="I512" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513">
+        <v>512</v>
+      </c>
+      <c r="B513" t="str">
+        <v>3/9/2026, 11:56:21 am</v>
+      </c>
+      <c r="C513" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D513" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E513" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F513" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G513" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-private-limited-hyderabad-7-to-12-years-180826931010</v>
+      </c>
+      <c r="H513" t="str">
+        <v/>
+      </c>
+      <c r="I513" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514">
+        <v>513</v>
+      </c>
+      <c r="B514" t="str">
+        <v>3/9/2026, 11:56:29 am</v>
+      </c>
+      <c r="C514" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D514" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E514" t="str">
+        <v>Tekskills</v>
+      </c>
+      <c r="F514" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G514" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-hyderabad-5-to-10-years-180826928300</v>
+      </c>
+      <c r="H514" t="str">
+        <v/>
+      </c>
+      <c r="I514" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515">
+        <v>514</v>
+      </c>
+      <c r="B515" t="str">
+        <v>3/9/2026, 11:56:37 am</v>
+      </c>
+      <c r="C515" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D515" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E515" t="str">
+        <v>TeamLease</v>
+      </c>
+      <c r="F515" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G515" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-teamlease-hyderabad-chennai-bengaluru-5-to-10-years-170826022750</v>
+      </c>
+      <c r="H515" t="str">
+        <v/>
+      </c>
+      <c r="I515" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516">
+        <v>515</v>
+      </c>
+      <c r="B516" t="str">
+        <v>3/9/2026, 11:56:45 am</v>
+      </c>
+      <c r="C516" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D516" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E516" t="str">
+        <v>Virtusa</v>
+      </c>
+      <c r="F516" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G516" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-virtusa-hyderabad-chennai-bengaluru-6-to-11-years-130826016398</v>
+      </c>
+      <c r="H516" t="str">
+        <v/>
+      </c>
+      <c r="I516" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517">
+        <v>516</v>
+      </c>
+      <c r="B517" t="str">
+        <v>3/9/2026, 11:56:53 am</v>
+      </c>
+      <c r="C517" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D517" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E517" t="str">
+        <v>Apexon</v>
+      </c>
+      <c r="F517" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G517" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-apexon-hyderabad-chennai-bengaluru-6-to-12-years-100826018539</v>
+      </c>
+      <c r="H517" t="str">
+        <v/>
+      </c>
+      <c r="I517" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518">
+        <v>517</v>
+      </c>
+      <c r="B518" t="str">
+        <v>3/9/2026, 11:57:01 am</v>
+      </c>
+      <c r="C518" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D518" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E518" t="str">
+        <v>ThoughtFocus</v>
+      </c>
+      <c r="F518" t="str">
+        <v>Hybrid - Hyderabad, Kochi</v>
+      </c>
+      <c r="G518" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-thoughtfocus-kochi-hyderabad-5-to-10-years-060826022891</v>
+      </c>
+      <c r="H518" t="str">
+        <v/>
+      </c>
+      <c r="I518" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519">
+        <v>518</v>
+      </c>
+      <c r="B519" t="str">
+        <v>3/9/2026, 11:57:09 am</v>
+      </c>
+      <c r="C519" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D519" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E519" t="str">
+        <v>Ilink Talent Solutions</v>
+      </c>
+      <c r="F519" t="str">
+        <v>Hyderabad, Pune, Chennai</v>
+      </c>
+      <c r="G519" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-ilink-talent-solutions-hyderabad-pune-chennai-5-to-10-years-050826028112</v>
+      </c>
+      <c r="H519" t="str">
+        <v/>
+      </c>
+      <c r="I519" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520">
+        <v>519</v>
+      </c>
+      <c r="B520" t="str">
+        <v>3/9/2026, 11:57:17 am</v>
+      </c>
+      <c r="C520" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D520" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E520" t="str">
+        <v>Synechron</v>
+      </c>
+      <c r="F520" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G520" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-synechron-hyderabad-pune-bengaluru-6-to-10-years-040826019957</v>
+      </c>
+      <c r="H520" t="str">
+        <v/>
+      </c>
+      <c r="I520" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521">
+        <v>520</v>
+      </c>
+      <c r="B521" t="str">
+        <v>3/9/2026, 11:57:25 am</v>
+      </c>
+      <c r="C521" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D521" t="str">
+        <v>Java Full Stack Developer - Hyderabad</v>
+      </c>
+      <c r="E521" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F521" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G521" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-hyderabad-infosys-hyderabad-5-to-9-years-290526023369</v>
+      </c>
+      <c r="H521" t="str">
+        <v/>
+      </c>
+      <c r="I521" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522">
+        <v>521</v>
+      </c>
+      <c r="B522" t="str">
+        <v>3/9/2026, 11:57:33 am</v>
+      </c>
+      <c r="C522" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D522" t="str">
+        <v>Java Full Stack Developer - Hyderabad</v>
+      </c>
+      <c r="E522" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F522" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G522" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-hyderabad-infosys-hyderabad-5-to-9-years-280526022017</v>
+      </c>
+      <c r="H522" t="str">
+        <v/>
+      </c>
+      <c r="I522" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523">
+        <v>522</v>
+      </c>
+      <c r="B523" t="str">
+        <v>3/9/2026, 11:57:41 am</v>
+      </c>
+      <c r="C523" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D523" t="str">
+        <v>Java Full Stack Developer - Hyderabad</v>
+      </c>
+      <c r="E523" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F523" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G523" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-hyderabad-infosys-hyderabad-5-to-9-years-280526012431</v>
+      </c>
+      <c r="H523" t="str">
+        <v/>
+      </c>
+      <c r="I523" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524">
+        <v>523</v>
+      </c>
+      <c r="B524" t="str">
+        <v>3/9/2026, 11:57:49 am</v>
+      </c>
+      <c r="C524" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D524" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E524" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F524" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G524" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tata-consultancy-services-hyderabad-pune-bengaluru-5-to-10-years-170826002918</v>
+      </c>
+      <c r="H524" t="str">
+        <v/>
+      </c>
+      <c r="I524" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525">
+        <v>524</v>
+      </c>
+      <c r="B525" t="str">
+        <v>3/9/2026, 11:57:57 am</v>
+      </c>
+      <c r="C525" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D525" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E525" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F525" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G525" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tata-consultancy-services-hyderabad-chennai-bengaluru-5-to-8-years-100826003076</v>
+      </c>
+      <c r="H525" t="str">
+        <v/>
+      </c>
+      <c r="I525" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526">
+        <v>525</v>
+      </c>
+      <c r="B526" t="str">
+        <v>3/9/2026, 11:58:05 am</v>
+      </c>
+      <c r="C526" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D526" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E526" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F526" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G526" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-infosys-hyderabad-chennai-bengaluru-4-to-9-years-080826015550</v>
+      </c>
+      <c r="H526" t="str">
+        <v/>
+      </c>
+      <c r="I526" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527">
+        <v>526</v>
+      </c>
+      <c r="B527" t="str">
+        <v>3/9/2026, 11:58:13 am</v>
+      </c>
+      <c r="C527" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D527" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E527" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F527" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G527" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-chennai-bengaluru-6-to-8-years-070826018206</v>
+      </c>
+      <c r="H527" t="str">
+        <v/>
+      </c>
+      <c r="I527" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528">
+        <v>527</v>
+      </c>
+      <c r="B528" t="str">
+        <v>3/9/2026, 11:58:21 am</v>
+      </c>
+      <c r="C528" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D528" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E528" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F528" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G528" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-pune-bengaluru-6-to-8-years-050826033493</v>
+      </c>
+      <c r="H528" t="str">
+        <v/>
+      </c>
+      <c r="I528" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529">
+        <v>528</v>
+      </c>
+      <c r="B529" t="str">
+        <v>3/9/2026, 11:58:29 am</v>
+      </c>
+      <c r="C529" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D529" t="str">
+        <v>Java Full-Stack Developer (Angular) - Hyderabad</v>
+      </c>
+      <c r="E529" t="str">
+        <v>Epam Systems</v>
+      </c>
+      <c r="F529" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G529" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-angular-hyderabad-epam-systems-hyderabad-10-to-14-years-030826007675</v>
+      </c>
+      <c r="H529" t="str">
+        <v/>
+      </c>
+      <c r="I529" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530">
+        <v>529</v>
+      </c>
+      <c r="B530" t="str">
+        <v>3/9/2026, 11:58:37 am</v>
+      </c>
+      <c r="C530" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D530" t="str">
+        <v>Java Full-Stack Developer (Angular) - Hyderabad</v>
+      </c>
+      <c r="E530" t="str">
+        <v>Epam Systems</v>
+      </c>
+      <c r="F530" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G530" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-angular-hyderabad-epam-systems-hyderabad-5-to-10-years-030826007552</v>
+      </c>
+      <c r="H530" t="str">
+        <v/>
+      </c>
+      <c r="I530" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531">
+        <v>530</v>
+      </c>
+      <c r="B531" t="str">
+        <v>3/9/2026, 11:58:45 am</v>
+      </c>
+      <c r="C531" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D531" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E531" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F531" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G531" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-chennai-bengaluru-6-to-8-years-030826005892</v>
+      </c>
+      <c r="H531" t="str">
+        <v/>
+      </c>
+      <c r="I531" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532">
+        <v>531</v>
+      </c>
+      <c r="B532" t="str">
+        <v>3/9/2026, 11:59:01 am</v>
+      </c>
+      <c r="C532" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D532" t="str">
+        <v>Java Full Stack Developer(angular)3-5 years-infosys</v>
+      </c>
+      <c r="E532" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F532" t="str">
+        <v>Hybrid - Hyderabad, Ahmedabad, Bengaluru</v>
+      </c>
+      <c r="G532" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-angular-3-5-years-infosys-infosys-hyderabad-ahmedabad-bengaluru-3-to-5-years-110326018473</v>
+      </c>
+      <c r="H532" t="str">
+        <v/>
+      </c>
+      <c r="I532" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533">
+        <v>532</v>
+      </c>
+      <c r="B533" t="str">
+        <v>3/9/2026, 11:59:09 am</v>
+      </c>
+      <c r="C533" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D533" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E533" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F533" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G533" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-infosys-limited-hyderabad-7-to-10-years-210826932584</v>
+      </c>
+      <c r="H533" t="str">
+        <v/>
+      </c>
+      <c r="I533" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534">
+        <v>533</v>
+      </c>
+      <c r="B534" t="str">
+        <v>3/9/2026, 11:59:17 am</v>
+      </c>
+      <c r="C534" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D534" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E534" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F534" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G534" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-private-limited-hyderabad-5-to-10-years-200826928351</v>
+      </c>
+      <c r="H534" t="str">
+        <v/>
+      </c>
+      <c r="I534" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535">
+        <v>534</v>
+      </c>
+      <c r="B535" t="str">
+        <v>3/9/2026, 11:59:25 am</v>
+      </c>
+      <c r="C535" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D535" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E535" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F535" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G535" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-india-private-limited-hyderabad-8-to-13-years-200826928259</v>
+      </c>
+      <c r="H535" t="str">
+        <v/>
+      </c>
+      <c r="I535" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536">
+        <v>535</v>
+      </c>
+      <c r="B536" t="str">
+        <v>3/9/2026, 11:59:33 am</v>
+      </c>
+      <c r="C536" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D536" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E536" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F536" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G536" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-infosys-hyderabad-chennai-bengaluru-5-to-10-years-200826034143</v>
+      </c>
+      <c r="H536" t="str">
+        <v/>
+      </c>
+      <c r="I536" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537">
+        <v>536</v>
+      </c>
+      <c r="B537" t="str">
+        <v>3/9/2026, 11:59:41 am</v>
+      </c>
+      <c r="C537" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D537" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E537" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F537" t="str">
+        <v>Hybrid - Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G537" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-pune-bengaluru-6-to-9-years-190826022729</v>
+      </c>
+      <c r="H537" t="str">
+        <v/>
+      </c>
+      <c r="I537" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538">
+        <v>537</v>
+      </c>
+      <c r="B538" t="str">
+        <v>3/9/2026, 11:59:49 am</v>
+      </c>
+      <c r="C538" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D538" t="str">
+        <v>Java Full Stack Developer | Angular/React Exp mandatory</v>
+      </c>
+      <c r="E538" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F538" t="str">
+        <v>Hybrid - Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G538" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-angular-react-exp-mandatory-capgemini-hyderabad-pune-bengaluru-6-to-9-years-100626014226</v>
+      </c>
+      <c r="H538" t="str">
+        <v/>
+      </c>
+      <c r="I538" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539">
+        <v>538</v>
+      </c>
+      <c r="B539" t="str">
+        <v>3/9/2026, 12:00:01 pm</v>
+      </c>
+      <c r="C539" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D539" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E539" t="str">
+        <v>Tekskills India</v>
+      </c>
+      <c r="F539" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G539" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-hyderabad-8-to-12-years-180826932307</v>
+      </c>
+      <c r="H539" t="str">
+        <v/>
+      </c>
+      <c r="I539" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540">
+        <v>539</v>
+      </c>
+      <c r="B540" t="str">
+        <v>3/9/2026, 12:00:09 pm</v>
+      </c>
+      <c r="C540" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D540" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E540" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F540" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G540" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-purview-india-consulting-and-services-llp-hyderabad-5-to-8-years-180826914445</v>
+      </c>
+      <c r="H540" t="str">
+        <v/>
+      </c>
+      <c r="I540" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541">
+        <v>540</v>
+      </c>
+      <c r="B541" t="str">
+        <v>3/9/2026, 12:00:17 pm</v>
+      </c>
+      <c r="C541" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D541" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E541" t="str">
+        <v>Innova Solutions</v>
+      </c>
+      <c r="F541" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G541" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-innova-solutions-hyderabad-chennai-bengaluru-10-to-20-years-180826048426</v>
+      </c>
+      <c r="H541" t="str">
+        <v/>
+      </c>
+      <c r="I541" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542">
+        <v>541</v>
+      </c>
+      <c r="B542" t="str">
+        <v>3/9/2026, 12:00:25 pm</v>
+      </c>
+      <c r="C542" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D542" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E542" t="str">
+        <v>Innova Solutions</v>
+      </c>
+      <c r="F542" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G542" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-innova-solutions-hyderabad-chennai-bengaluru-7-to-12-years-180826048404</v>
+      </c>
+      <c r="H542" t="str">
+        <v/>
+      </c>
+      <c r="I542" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543">
+        <v>542</v>
+      </c>
+      <c r="B543" t="str">
+        <v>3/9/2026, 12:00:33 pm</v>
+      </c>
+      <c r="C543" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D543" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E543" t="str">
+        <v>Cloudxtreme</v>
+      </c>
+      <c r="F543" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G543" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cloudxtreme-hyderabad-bengaluru-5-to-8-years-180826026372</v>
+      </c>
+      <c r="H543" t="str">
+        <v/>
+      </c>
+      <c r="I543" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544">
+        <v>543</v>
+      </c>
+      <c r="B544" t="str">
+        <v>3/9/2026, 12:00:41 pm</v>
+      </c>
+      <c r="C544" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D544" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E544" t="str">
+        <v>Deloitte US-India Offices</v>
+      </c>
+      <c r="F544" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G544" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-deloitte-us-india-offices-hyderabad-pune-bengaluru-4-to-7-years-130826023761</v>
+      </c>
+      <c r="H544" t="str">
+        <v/>
+      </c>
+      <c r="I544" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545">
+        <v>544</v>
+      </c>
+      <c r="B545" t="str">
+        <v>3/9/2026, 12:00:49 pm</v>
+      </c>
+      <c r="C545" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D545" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E545" t="str">
+        <v>Persistent</v>
+      </c>
+      <c r="F545" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G545" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-persistent-hyderabad-bengaluru-5-to-8-years-120826016102</v>
+      </c>
+      <c r="H545" t="str">
+        <v/>
+      </c>
+      <c r="I545" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546">
+        <v>545</v>
+      </c>
+      <c r="B546" t="str">
+        <v>3/9/2026, 12:00:57 pm</v>
+      </c>
+      <c r="C546" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D546" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E546" t="str">
+        <v>Deloitte US-India Offices</v>
+      </c>
+      <c r="F546" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G546" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-deloitte-us-india-offices-hyderabad-pune-bengaluru-4-to-7-years-060826025165</v>
+      </c>
+      <c r="H546" t="str">
+        <v/>
+      </c>
+      <c r="I546" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547">
+        <v>546</v>
+      </c>
+      <c r="B547" t="str">
+        <v>3/9/2026, 12:01:05 pm</v>
+      </c>
+      <c r="C547" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D547" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E547" t="str">
+        <v>Leading IT MNC</v>
+      </c>
+      <c r="F547" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G547" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-leinex-consulting-hyderabad-4-to-9-years-060826017910</v>
+      </c>
+      <c r="H547" t="str">
+        <v/>
+      </c>
+      <c r="I547" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548">
+        <v>547</v>
+      </c>
+      <c r="B548" t="str">
+        <v>3/9/2026, 12:01:13 pm</v>
+      </c>
+      <c r="C548" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D548" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E548" t="str">
+        <v>Tekskills india pvt ltd</v>
+      </c>
+      <c r="F548" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G548" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tekskills-hyderabad-chennai-bengaluru-7-to-10-years-050826021428</v>
+      </c>
+      <c r="H548" t="str">
+        <v/>
+      </c>
+      <c r="I548" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549">
+        <v>548</v>
+      </c>
+      <c r="B549" t="str">
+        <v>3/9/2026, 12:01:21 pm</v>
+      </c>
+      <c r="C549" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D549" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E549" t="str">
+        <v>Virtusa</v>
+      </c>
+      <c r="F549" t="str">
+        <v>Hybrid - Hyderabad, Pune, Chennai</v>
+      </c>
+      <c r="G549" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-virtusa-hyderabad-pune-chennai-9-to-14-years-040826033699</v>
+      </c>
+      <c r="H549" t="str">
+        <v/>
+      </c>
+      <c r="I549" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550">
+        <v>549</v>
+      </c>
+      <c r="B550" t="str">
+        <v>3/9/2026, 12:01:33 pm</v>
+      </c>
+      <c r="C550" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D550" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E550" t="str">
+        <v>Coforge</v>
+      </c>
+      <c r="F550" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G550" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-coforge-hyderabad-5-to-8-years-120826041703</v>
+      </c>
+      <c r="H550" t="str">
+        <v/>
+      </c>
+      <c r="I550" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551">
+        <v>550</v>
+      </c>
+      <c r="B551" t="str">
+        <v>3/9/2026, 12:01:41 pm</v>
+      </c>
+      <c r="C551" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D551" t="str">
+        <v>Java Full Stack Developer - F2F - 22nd Aug</v>
+      </c>
+      <c r="E551" t="str">
+        <v>Hirexa Solutions</v>
+      </c>
+      <c r="F551" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G551" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-f2f-22nd-aug-hirexa-solutions-hyderabad-4-to-7-years-120826015731</v>
+      </c>
+      <c r="H551" t="str">
+        <v/>
+      </c>
+      <c r="I551" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552">
+        <v>551</v>
+      </c>
+      <c r="B552" t="str">
+        <v>3/9/2026, 12:01:49 pm</v>
+      </c>
+      <c r="C552" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D552" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E552" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F552" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G552" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-pune-bengaluru-6-to-8-years-070826022851</v>
+      </c>
+      <c r="H552" t="str">
+        <v/>
+      </c>
+      <c r="I552" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553">
+        <v>552</v>
+      </c>
+      <c r="B553" t="str">
+        <v>3/9/2026, 12:02:01 pm</v>
+      </c>
+      <c r="C553" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D553" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E553" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F553" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G553" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-tata-consultancy-services-hyderabad-chennai-bengaluru-5-to-10-years-060826026647</v>
+      </c>
+      <c r="H553" t="str">
+        <v/>
+      </c>
+      <c r="I553" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554">
+        <v>553</v>
+      </c>
+      <c r="B554" t="str">
+        <v>3/9/2026, 12:02:09 pm</v>
+      </c>
+      <c r="C554" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D554" t="str">
+        <v>Java Full Stack Developer - Hyderabad - B</v>
+      </c>
+      <c r="E554" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F554" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G554" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-hyderabad-b-infosys-hyderabad-5-to-9-years-060726011615</v>
+      </c>
+      <c r="H554" t="str">
+        <v/>
+      </c>
+      <c r="I554" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555">
+        <v>554</v>
+      </c>
+      <c r="B555" t="str">
+        <v>3/9/2026, 12:02:17 pm</v>
+      </c>
+      <c r="C555" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D555" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E555" t="str">
+        <v>Capgemini</v>
+      </c>
+      <c r="F555" t="str">
+        <v>Hybrid - Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G555" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-capgemini-hyderabad-bengaluru-5-to-8-years-050826010667</v>
+      </c>
+      <c r="H555" t="str">
+        <v/>
+      </c>
+      <c r="I555" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556">
+        <v>555</v>
+      </c>
+      <c r="B556" t="str">
+        <v>3/9/2026, 12:02:26 pm</v>
+      </c>
+      <c r="C556" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D556" t="str">
+        <v>Java Full Stack Developer</v>
+      </c>
+      <c r="E556" t="str">
+        <v>Pragma Edge Software Services</v>
+      </c>
+      <c r="F556" t="str">
+        <v>Hyderabad, Bengaluru, Delhi / NCR</v>
+      </c>
+      <c r="G556" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-pragma-edge-software-services-hyderabad-bengaluru-delhi-ncr-4-to-7-years-050826006259</v>
+      </c>
+      <c r="H556" t="str">
+        <v/>
+      </c>
+      <c r="I556" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557">
+        <v>556</v>
+      </c>
+      <c r="B557" t="str">
+        <v>3/9/2026, 12:02:42 pm</v>
+      </c>
+      <c r="C557" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D557" t="str">
+        <v>Senior Core Java Full Stack Developer (Big Data)</v>
+      </c>
+      <c r="E557" t="str">
+        <v>Tek Ninjas</v>
+      </c>
+      <c r="F557" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G557" t="str">
+        <v>https://www.naukri.com/job-listings-senior-core-java-full-stack-developer-big-data-tek-ninjas-hyderabad-8-to-13-years-060826015518</v>
+      </c>
+      <c r="H557" t="str">
+        <v/>
+      </c>
+      <c r="I557" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558">
+        <v>557</v>
+      </c>
+      <c r="B558" t="str">
+        <v>3/9/2026, 12:02:50 pm</v>
+      </c>
+      <c r="C558" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D558" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E558" t="str">
+        <v>MY Guru Knowledge Center</v>
+      </c>
+      <c r="F558" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G558" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-my-guru-knowledge-center-private-limited-hyderabad-2-to-7-years-020926930988</v>
+      </c>
+      <c r="H558" t="str">
+        <v/>
+      </c>
+      <c r="I558" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559">
+        <v>558</v>
+      </c>
+      <c r="B559" t="str">
+        <v>3/9/2026, 12:02:58 pm</v>
+      </c>
+      <c r="C559" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D559" t="str">
+        <v>Java Spring Boot Developer</v>
+      </c>
+      <c r="E559" t="str">
+        <v>Tekskills India pvt ltd</v>
+      </c>
+      <c r="F559" t="str">
+        <v>Hybrid - Hyderabad, pan india</v>
+      </c>
+      <c r="G559" t="str">
+        <v>https://www.naukri.com/job-listings-java-spring-boot-developer-tekskills-hyderabad-pan-india-6-to-11-years-180826934193</v>
+      </c>
+      <c r="H559" t="str">
+        <v/>
+      </c>
+      <c r="I559" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560">
+        <v>559</v>
+      </c>
+      <c r="B560" t="str">
+        <v>3/9/2026, 12:03:06 pm</v>
+      </c>
+      <c r="C560" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D560" t="str">
+        <v>Hiring Java Full Stack Developer</v>
+      </c>
+      <c r="E560" t="str">
+        <v>Motivity Labs</v>
+      </c>
+      <c r="F560" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G560" t="str">
+        <v>https://www.naukri.com/job-listings-hiring-java-full-stack-developer-motivity-labs-hyderabad-5-to-10-years-300924003203</v>
+      </c>
+      <c r="H560" t="str">
+        <v/>
+      </c>
+      <c r="I560" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561">
+        <v>560</v>
+      </c>
+      <c r="B561" t="str">
+        <v>3/9/2026, 12:03:14 pm</v>
+      </c>
+      <c r="C561" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D561" t="str">
+        <v>Java Full Stack Developer ( 7+yrs)</v>
+      </c>
+      <c r="E561" t="str">
+        <v>Sunware Technologies</v>
+      </c>
+      <c r="F561" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G561" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-7-yrs-sunware-technologies-hyderabad-chennai-bengaluru-8-to-13-years-020926026062</v>
+      </c>
+      <c r="H561" t="str">
+        <v/>
+      </c>
+      <c r="I561" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562">
+        <v>561</v>
+      </c>
+      <c r="B562" t="str">
+        <v>3/9/2026, 12:03:22 pm</v>
+      </c>
+      <c r="C562" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D562" t="str">
+        <v>Java Back End Developer</v>
+      </c>
+      <c r="E562" t="str">
+        <v>Zclus India</v>
+      </c>
+      <c r="F562" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G562" t="str">
+        <v>https://www.naukri.com/job-listings-java-back-end-developer-zclus-india-hyderabad-3-to-8-years-030926011104</v>
+      </c>
+      <c r="H562" t="str">
+        <v/>
+      </c>
+      <c r="I562" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563">
+        <v>562</v>
+      </c>
+      <c r="B563" t="str">
+        <v>3/9/2026, 12:03:27 pm</v>
+      </c>
+      <c r="C563" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D563" t="str">
+        <v>Walk-in || Java Full Stack Developer with React JS</v>
+      </c>
+      <c r="E563" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F563" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G563" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-with-react-js-tata-consultancy-services-hyderabad-7-to-10-years-020926030197</v>
+      </c>
+      <c r="H563" t="str">
+        <v/>
+      </c>
+      <c r="I563" t="str">
+        <v>no_apply_button</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564">
+        <v>563</v>
+      </c>
+      <c r="B564" t="str">
+        <v>3/9/2026, 12:03:39 pm</v>
+      </c>
+      <c r="C564" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D564" t="str">
+        <v>Software Engineer 2</v>
+      </c>
+      <c r="E564" t="str">
+        <v>Highradius</v>
+      </c>
+      <c r="F564" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G564" t="str">
+        <v>https://www.naukri.com/job-listings-software-engineer-2-highradius-hyderabad-3-to-5-years-020926012409</v>
+      </c>
+      <c r="H564" t="str">
+        <v/>
+      </c>
+      <c r="I564" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565">
+        <v>564</v>
+      </c>
+      <c r="B565" t="str">
+        <v>3/9/2026, 12:03:47 pm</v>
+      </c>
+      <c r="C565" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D565" t="str">
+        <v>Senior full stack (Java + React) Developer</v>
+      </c>
+      <c r="E565" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F565" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G565" t="str">
+        <v>https://www.naukri.com/job-listings-senior-full-stack-java-react-developer-tata-consultancy-services-hyderabad-7-to-11-years-210826004285</v>
+      </c>
+      <c r="H565" t="str">
+        <v/>
+      </c>
+      <c r="I565" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566">
+        <v>565</v>
+      </c>
+      <c r="B566" t="str">
+        <v>3/9/2026, 12:03:59 pm</v>
+      </c>
+      <c r="C566" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D566" t="str">
+        <v>Java Developer (2-9 y)</v>
+      </c>
+      <c r="E566" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F566" t="str">
+        <v>Hybrid - Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G566" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-2-9-y-infosys-hyderabad-pune-bengaluru-2-to-7-years-020926034338</v>
+      </c>
+      <c r="H566" t="str">
+        <v/>
+      </c>
+      <c r="I566" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567">
+        <v>566</v>
+      </c>
+      <c r="B567" t="str">
+        <v>3/9/2026, 12:04:11 pm</v>
+      </c>
+      <c r="C567" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D567" t="str">
+        <v>Java Backend Engineer</v>
+      </c>
+      <c r="E567" t="str">
+        <v>Ascendion Engineering</v>
+      </c>
+      <c r="F567" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G567" t="str">
+        <v>https://www.naukri.com/job-listings-java-backend-engineer-ascendion-engineering-hyderabad-bengaluru-10-to-15-years-020926027824</v>
+      </c>
+      <c r="H567" t="str">
+        <v/>
+      </c>
+      <c r="I567" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568">
+        <v>567</v>
+      </c>
+      <c r="B568" t="str">
+        <v>3/9/2026, 12:04:19 pm</v>
+      </c>
+      <c r="C568" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D568" t="str">
+        <v>Senior Software Engineer</v>
+      </c>
+      <c r="E568" t="str">
+        <v>Epam Systems</v>
+      </c>
+      <c r="F568" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G568" t="str">
+        <v>https://www.naukri.com/job-listings-senior-software-engineer-epam-systems-hyderabad-pune-bengaluru-5-to-10-years-020926022605</v>
+      </c>
+      <c r="H568" t="str">
+        <v/>
+      </c>
+      <c r="I568" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569">
+        <v>568</v>
+      </c>
+      <c r="B569" t="str">
+        <v>3/9/2026, 12:04:27 pm</v>
+      </c>
+      <c r="C569" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D569" t="str">
+        <v>Full Stack Engineer (Angular with Java)</v>
+      </c>
+      <c r="E569" t="str">
+        <v>Solugenix</v>
+      </c>
+      <c r="F569" t="str">
+        <v>Hybrid - Hyderabad, Indore, Bengaluru</v>
+      </c>
+      <c r="G569" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-engineer-angular-with-java-solugenix-indore-hyderabad-bengaluru-3-to-5-years-020926033769</v>
+      </c>
+      <c r="H569" t="str">
+        <v/>
+      </c>
+      <c r="I569" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570">
+        <v>569</v>
+      </c>
+      <c r="B570" t="str">
+        <v>3/9/2026, 12:04:35 pm</v>
+      </c>
+      <c r="C570" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D570" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E570" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F570" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G570" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-tata-consultancy-services-hyderabad-chennai-bengaluru-5-to-10-years-020926022271</v>
+      </c>
+      <c r="H570" t="str">
+        <v/>
+      </c>
+      <c r="I570" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571">
+        <v>570</v>
+      </c>
+      <c r="B571" t="str">
+        <v>3/9/2026, 12:04:43 pm</v>
+      </c>
+      <c r="C571" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D571" t="str">
+        <v>Java_Springboot_Microservice (3-5 Years)</v>
+      </c>
+      <c r="E571" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F571" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G571" t="str">
+        <v>https://www.naukri.com/job-listings-java-springboot-microservice-3-5-years-infosys-hyderabad-chennai-bengaluru-3-to-5-years-290726029995</v>
+      </c>
+      <c r="H571" t="str">
+        <v/>
+      </c>
+      <c r="I571" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572">
+        <v>571</v>
+      </c>
+      <c r="B572" t="str">
+        <v>3/9/2026, 12:04:51 pm</v>
+      </c>
+      <c r="C572" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D572" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E572" t="str">
+        <v>Tanisha Systems</v>
+      </c>
+      <c r="F572" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G572" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-tanisha-systems-hyderabad-5-to-10-years-020926022470</v>
+      </c>
+      <c r="H572" t="str">
+        <v/>
+      </c>
+      <c r="I572" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573">
+        <v>572</v>
+      </c>
+      <c r="B573" t="str">
+        <v>3/9/2026, 12:04:55 pm</v>
+      </c>
+      <c r="C573" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D573" t="str">
+        <v>Walk-in || Java Developer</v>
+      </c>
+      <c r="E573" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F573" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G573" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-tata-consultancy-services-hyderabad-6-to-10-years-020926026639</v>
+      </c>
+      <c r="H573" t="str">
+        <v/>
+      </c>
+      <c r="I573" t="str">
+        <v>no_apply_button</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574">
+        <v>573</v>
+      </c>
+      <c r="B574" t="str">
+        <v>3/9/2026, 12:04:59 pm</v>
+      </c>
+      <c r="C574" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D574" t="str">
+        <v>Walk-in || Java Developer</v>
+      </c>
+      <c r="E574" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F574" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G574" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-tata-consultancy-services-hyderabad-6-to-11-years-020926025738</v>
+      </c>
+      <c r="H574" t="str">
+        <v/>
+      </c>
+      <c r="I574" t="str">
+        <v>no_apply_button</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575">
+        <v>574</v>
+      </c>
+      <c r="B575" t="str">
+        <v>3/9/2026, 12:05:08 pm</v>
+      </c>
+      <c r="C575" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D575" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E575" t="str">
+        <v>Persistent</v>
+      </c>
+      <c r="F575" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G575" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-persistent-hyderabad-bengaluru-6-to-10-years-020926018032</v>
+      </c>
+      <c r="H575" t="str">
+        <v/>
+      </c>
+      <c r="I575" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576">
+        <v>575</v>
+      </c>
+      <c r="B576" t="str">
+        <v>3/9/2026, 12:05:16 pm</v>
+      </c>
+      <c r="C576" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D576" t="str">
+        <v>Java Developer | Walkin Interview</v>
+      </c>
+      <c r="E576" t="str">
+        <v>Leading Technology Company</v>
+      </c>
+      <c r="F576" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G576" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-walkin-interview-sp-staffing-hyderabad-5-to-10-years-020926024156</v>
+      </c>
+      <c r="H576" t="str">
+        <v/>
+      </c>
+      <c r="I576" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577">
+        <v>576</v>
+      </c>
+      <c r="B577" t="str">
+        <v>3/9/2026, 12:05:24 pm</v>
+      </c>
+      <c r="C577" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D577" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E577" t="str">
+        <v>Wipro</v>
+      </c>
+      <c r="F577" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G577" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-infinityquest-it-services-hyderabad-chennai-bengaluru-8-to-13-years-030926007507</v>
+      </c>
+      <c r="H577" t="str">
+        <v/>
+      </c>
+      <c r="I577" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578">
+        <v>577</v>
+      </c>
+      <c r="B578" t="str">
+        <v>3/9/2026, 12:05:32 pm</v>
+      </c>
+      <c r="C578" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D578" t="str">
+        <v>Java Developer - Remote</v>
+      </c>
+      <c r="E578" t="str">
+        <v>Magnify360 Hi-tech Solutions</v>
+      </c>
+      <c r="F578" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G578" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-remote-magnify360-hi-tech-solutions-hyderabad-pune-bengaluru-9-to-12-years-020926022474</v>
+      </c>
+      <c r="H578" t="str">
+        <v/>
+      </c>
+      <c r="I578" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579">
+        <v>578</v>
+      </c>
+      <c r="B579" t="str">
+        <v>3/9/2026, 12:05:40 pm</v>
+      </c>
+      <c r="C579" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D579" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E579" t="str">
+        <v>Ascendion</v>
+      </c>
+      <c r="F579" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G579" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-ascendion-engineering-hyderabad-8-to-13-years-020926011926</v>
+      </c>
+      <c r="H579" t="str">
+        <v/>
+      </c>
+      <c r="I579" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580">
+        <v>579</v>
+      </c>
+      <c r="B580" t="str">
+        <v>3/9/2026, 12:05:48 pm</v>
+      </c>
+      <c r="C580" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D580" t="str">
+        <v>Java Developer with GCP</v>
+      </c>
+      <c r="E580" t="str">
+        <v>Persistent</v>
+      </c>
+      <c r="F580" t="str">
+        <v>Hyderabad, Pune</v>
+      </c>
+      <c r="G580" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-with-gcp-persistent-hyderabad-pune-8-to-17-years-030926007035</v>
+      </c>
+      <c r="H580" t="str">
+        <v/>
+      </c>
+      <c r="I580" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581">
+        <v>580</v>
+      </c>
+      <c r="B581" t="str">
+        <v>3/9/2026, 12:05:57 pm</v>
+      </c>
+      <c r="C581" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D581" t="str">
+        <v>Java Kafka Developer</v>
+      </c>
+      <c r="E581" t="str">
+        <v>Virtusa</v>
+      </c>
+      <c r="F581" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G581" t="str">
+        <v>https://www.naukri.com/job-listings-java-kafka-developer-virtusa-hyderabad-6-to-10-years-020926036313</v>
+      </c>
+      <c r="H581" t="str">
+        <v/>
+      </c>
+      <c r="I581" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582">
+        <v>581</v>
+      </c>
+      <c r="B582" t="str">
+        <v>3/9/2026, 12:06:05 pm</v>
+      </c>
+      <c r="C582" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D582" t="str">
+        <v>Job opportunity of Java Developer-Hyderabad Location !!</v>
+      </c>
+      <c r="E582" t="str">
+        <v>Virtusa</v>
+      </c>
+      <c r="F582" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G582" t="str">
+        <v>https://www.naukri.com/job-listings-opportunity-of-java-developer-hyderabad-location-virtusa-hyderabad-7-to-10-years-050826037734</v>
+      </c>
+      <c r="H582" t="str">
+        <v/>
+      </c>
+      <c r="I582" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583">
+        <v>582</v>
+      </c>
+      <c r="B583" t="str">
+        <v>3/9/2026, 12:06:13 pm</v>
+      </c>
+      <c r="C583" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D583" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E583" t="str">
+        <v>Cloudxtreme</v>
+      </c>
+      <c r="F583" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G583" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-cloudxtreme-hyderabad-bengaluru-5-to-10-years-030826013209</v>
+      </c>
+      <c r="H583" t="str">
+        <v/>
+      </c>
+      <c r="I583" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584">
+        <v>583</v>
+      </c>
+      <c r="B584" t="str">
+        <v>3/9/2026, 12:06:21 pm</v>
+      </c>
+      <c r="C584" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D584" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E584" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F584" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G584" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-tata-consultancy-services-hyderabad-chennai-bengaluru-6-to-11-years-300626033970</v>
+      </c>
+      <c r="H584" t="str">
+        <v/>
+      </c>
+      <c r="I584" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585">
+        <v>584</v>
+      </c>
+      <c r="B585" t="str">
+        <v>3/9/2026, 12:06:29 pm</v>
+      </c>
+      <c r="C585" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D585" t="str">
+        <v>Java Developer + React - Hyderabad</v>
+      </c>
+      <c r="E585" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F585" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G585" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-react-hyderabad-infosys-hyderabad-5-to-10-years-280526028415</v>
+      </c>
+      <c r="H585" t="str">
+        <v/>
+      </c>
+      <c r="I585" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586">
+        <v>585</v>
+      </c>
+      <c r="B586" t="str">
+        <v>3/9/2026, 12:06:49 pm</v>
+      </c>
+      <c r="C586" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D586" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E586" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F586" t="str">
+        <v>Hyderabad, Pune, Bengaluru</v>
+      </c>
+      <c r="G586" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-infosys-hyderabad-pune-bengaluru-5-to-9-years-100826001331</v>
+      </c>
+      <c r="H586" t="str">
+        <v/>
+      </c>
+      <c r="I586" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587">
+        <v>586</v>
+      </c>
+      <c r="B587" t="str">
+        <v>3/9/2026, 12:07:01 pm</v>
+      </c>
+      <c r="C587" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D587" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E587" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F587" t="str">
+        <v>Hybrid - Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G587" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-infosys-hyderabad-chennai-bengaluru-5-to-9-years-060326030692</v>
+      </c>
+      <c r="H587" t="str">
+        <v/>
+      </c>
+      <c r="I587" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588">
+        <v>587</v>
+      </c>
+      <c r="B588" t="str">
+        <v>3/9/2026, 12:07:09 pm</v>
+      </c>
+      <c r="C588" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D588" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E588" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F588" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G588" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-tata-consultancy-services-hyderabad-chennai-bengaluru-6-to-11-years-040826021308</v>
+      </c>
+      <c r="H588" t="str">
+        <v/>
+      </c>
+      <c r="I588" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589">
+        <v>588</v>
+      </c>
+      <c r="B589" t="str">
+        <v>3/9/2026, 12:07:17 pm</v>
+      </c>
+      <c r="C589" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D589" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E589" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F589" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G589" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-leading-client-hyderabad-8-to-13-years-030826909933</v>
+      </c>
+      <c r="H589" t="str">
+        <v/>
+      </c>
+      <c r="I589" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590">
+        <v>589</v>
+      </c>
+      <c r="B590" t="str">
+        <v>3/9/2026, 12:07:25 pm</v>
+      </c>
+      <c r="C590" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D590" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E590" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F590" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G590" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-infosys-hyderabad-chennai-bengaluru-5-to-9-years-030726026038</v>
+      </c>
+      <c r="H590" t="str">
+        <v/>
+      </c>
+      <c r="I590" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591">
+        <v>590</v>
+      </c>
+      <c r="B591" t="str">
+        <v>3/9/2026, 12:07:33 pm</v>
+      </c>
+      <c r="C591" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D591" t="str">
+        <v>Java Weblogic Developer</v>
+      </c>
+      <c r="E591" t="str">
+        <v>Akshaya Business It Solutions</v>
+      </c>
+      <c r="F591" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G591" t="str">
+        <v>https://www.naukri.com/job-listings-java-weblogic-developer-akshaya-business-it-solutions-hyderabad-5-to-10-years-250826025897</v>
+      </c>
+      <c r="H591" t="str">
+        <v/>
+      </c>
+      <c r="I591" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592">
+        <v>591</v>
+      </c>
+      <c r="B592" t="str">
+        <v>3/9/2026, 12:07:41 pm</v>
+      </c>
+      <c r="C592" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D592" t="str">
+        <v>Java Developer with GCP</v>
+      </c>
+      <c r="E592" t="str">
+        <v>Raj Consultancy</v>
+      </c>
+      <c r="F592" t="str">
+        <v>Hyderabad, Pune</v>
+      </c>
+      <c r="G592" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-with-gcp-raj-consultancy-hyderabad-pune-5-to-8-years-130826014982</v>
+      </c>
+      <c r="H592" t="str">
+        <v/>
+      </c>
+      <c r="I592" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593">
+        <v>592</v>
+      </c>
+      <c r="B593" t="str">
+        <v>3/9/2026, 12:07:49 pm</v>
+      </c>
+      <c r="C593" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D593" t="str">
+        <v>Java Developer with Azure</v>
+      </c>
+      <c r="E593" t="str">
+        <v>Hiring for Leading MNC Company!!</v>
+      </c>
+      <c r="F593" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G593" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-with-azure-sp-staffing-hyderabad-5-to-10-years-110826014155</v>
+      </c>
+      <c r="H593" t="str">
+        <v/>
+      </c>
+      <c r="I593" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594">
+        <v>593</v>
+      </c>
+      <c r="B594" t="str">
+        <v>3/9/2026, 12:07:57 pm</v>
+      </c>
+      <c r="C594" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D594" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E594" t="str">
+        <v>People Prime Worldwide</v>
+      </c>
+      <c r="F594" t="str">
+        <v>Hyderabad, Noida, Gurugram</v>
+      </c>
+      <c r="G594" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-people-prime-worldwide-noida-hyderabad-gurugram-8-to-15-years-140826019237</v>
+      </c>
+      <c r="H594" t="str">
+        <v/>
+      </c>
+      <c r="I594" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595">
+        <v>594</v>
+      </c>
+      <c r="B595" t="str">
+        <v>3/9/2026, 12:08:05 pm</v>
+      </c>
+      <c r="C595" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D595" t="str">
+        <v>Java Developer with GCP</v>
+      </c>
+      <c r="E595" t="str">
+        <v>Hiring for Leading MNC Company!!</v>
+      </c>
+      <c r="F595" t="str">
+        <v>Hybrid - Hyderabad</v>
+      </c>
+      <c r="G595" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-with-gcp-sp-staffing-hyderabad-5-to-10-years-110826014261</v>
+      </c>
+      <c r="H595" t="str">
+        <v/>
+      </c>
+      <c r="I595" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596">
+        <v>595</v>
+      </c>
+      <c r="B596" t="str">
+        <v>3/9/2026, 12:08:13 pm</v>
+      </c>
+      <c r="C596" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D596" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E596" t="str">
+        <v>Bright Technologies</v>
+      </c>
+      <c r="F596" t="str">
+        <v>Hybrid - Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G596" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-bright-academy-marathalli-hyderabad-bengaluru-5-to-10-years-020826005116</v>
+      </c>
+      <c r="H596" t="str">
+        <v/>
+      </c>
+      <c r="I596" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597">
+        <v>596</v>
+      </c>
+      <c r="B597" t="str">
+        <v>3/9/2026, 12:08:25 pm</v>
+      </c>
+      <c r="C597" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D597" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E597" t="str">
+        <v>Epam Systems</v>
+      </c>
+      <c r="F597" t="str">
+        <v>Hyderabad, Bengaluru</v>
+      </c>
+      <c r="G597" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-epam-systems-hyderabad-bengaluru-4-to-9-years-060826014010</v>
+      </c>
+      <c r="H597" t="str">
+        <v/>
+      </c>
+      <c r="I597" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598">
+        <v>597</v>
+      </c>
+      <c r="B598" t="str">
+        <v>3/9/2026, 12:08:34 pm</v>
+      </c>
+      <c r="C598" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D598" t="str">
+        <v>Urgent Hiring || Java Developer ||</v>
+      </c>
+      <c r="E598" t="str">
+        <v>Eniac Systems</v>
+      </c>
+      <c r="F598" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G598" t="str">
+        <v>https://www.naukri.com/job-listings-urgent-hiring-java-developer-eniac-systems-hyderabad-7-to-12-years-050826021548</v>
+      </c>
+      <c r="H598" t="str">
+        <v/>
+      </c>
+      <c r="I598" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599">
+        <v>598</v>
+      </c>
+      <c r="B599" t="str">
+        <v>3/9/2026, 12:08:50 pm</v>
+      </c>
+      <c r="C599" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D599" t="str">
+        <v>React.js Developer</v>
+      </c>
+      <c r="E599" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F599" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G599" t="str">
+        <v>https://www.naukri.com/job-listings-react-js-developer-infosys-limited-hyderabad-2-to-3-years-040826909383</v>
+      </c>
+      <c r="H599" t="str">
+        <v/>
+      </c>
+      <c r="I599" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600">
+        <v>599</v>
+      </c>
+      <c r="B600" t="str">
+        <v>3/9/2026, 12:08:57 pm</v>
+      </c>
+      <c r="C600" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D600" t="str">
+        <v>React JS Developer - INF (2-3) YRS</v>
+      </c>
+      <c r="E600" t="str">
+        <v>Infosys</v>
+      </c>
+      <c r="F600" t="str">
+        <v>Hyderabad, Chennai, Bengaluru</v>
+      </c>
+      <c r="G600" t="str">
+        <v>https://www.naukri.com/job-listings-react-js-developer-inf-2-3-yrs-infosys-hyderabad-chennai-bengaluru-2-to-3-years-200826032870</v>
+      </c>
+      <c r="H600" t="str">
+        <v/>
+      </c>
+      <c r="I600" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I419"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I600"/>
   </ignoredErrors>
 </worksheet>
 </file>